--- a/personetics-demo-data.xlsx
+++ b/personetics-demo-data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="462">
   <si>
     <t>Chapter</t>
   </si>
@@ -44,88 +44,373 @@
     <t>Business Lenses</t>
   </si>
   <si>
-    <t>Smart Start Account and GAA Savings Goal</t>
-  </si>
-  <si>
-    <t>Parents deposit weekly pocket money into Paul's Smart Start Account</t>
-  </si>
-  <si>
-    <t>Age 11</t>
+    <t>Birth</t>
+  </si>
+  <si>
+    <t>A family account is opened</t>
   </si>
   <si>
     <t>childhood</t>
   </si>
   <si>
-    <t>Confidence and Motivation</t>
-  </si>
-  <si>
-    <t>Paul is 11, loves sport, and mostly spends on GAA gear. BOI Buddy turns pocket money deposits into an achievable savings habit tied to his birthday goal.</t>
-  </si>
-  <si>
-    <t>Balance Growth, Engagement Lift, Financial Health, Primacy</t>
-  </si>
-  <si>
-    <t>Transition to Student Account</t>
-  </si>
-  <si>
-    <t>BOI Buddy recommends moving from Smart Start to Student Account</t>
-  </si>
-  <si>
-    <t>Age 17</t>
+    <t>New Beginnings</t>
+  </si>
+  <si>
+    <t>Alex's parents open a child savings account at Hero Bank — the first thread in a lifetime relationship.</t>
+  </si>
+  <si>
+    <t>Balance Growth, Engagement Lift</t>
+  </si>
+  <si>
+    <t>Becoming a teenager</t>
+  </si>
+  <si>
+    <t>First debit card issued</t>
+  </si>
+  <si>
+    <t>Age 16</t>
+  </si>
+  <si>
+    <t>Independence</t>
+  </si>
+  <si>
+    <t>Alex gets a first debit card. Every swipe is a chance to teach a money habit that lasts a lifetime.</t>
+  </si>
+  <si>
+    <t>Engagement Lift, Financial Health, Primacy</t>
+  </si>
+  <si>
+    <t>Leaving home for college</t>
+  </si>
+  <si>
+    <t>Tuition payments and student spending begin</t>
+  </si>
+  <si>
+    <t>Age 18</t>
   </si>
   <si>
     <t>student</t>
   </si>
   <si>
-    <t>Readiness and Independence</t>
-  </si>
-  <si>
-    <t>Paul is now 17 and transitioning to a Student Account. BOI Buddy analyzes his savings behavior and introduces a simple budget for driving lessons or college fees.</t>
-  </si>
-  <si>
-    <t>Primacy, Engagement Lift, Financial Health, Retention</t>
-  </si>
-  <si>
-    <t>Early Career Salary-Rent Cycle</t>
-  </si>
-  <si>
-    <t>Monthly salary arrives and rent exits, triggering mortgage saver recommendation</t>
+    <t>New Chapter</t>
+  </si>
+  <si>
+    <t>Tuition, books, dorm — Alex's life turns financially complex overnight. MyBank steadies the ride.</t>
+  </si>
+  <si>
+    <t>Building credit</t>
+  </si>
+  <si>
+    <t>First credit card opened</t>
+  </si>
+  <si>
+    <t>Age 19</t>
+  </si>
+  <si>
+    <t>Building Credit</t>
+  </si>
+  <si>
+    <t>Alex opens a student credit card. MyBank teaches the hidden rules of credit before the first mistake.</t>
+  </si>
+  <si>
+    <t>Credit Growth, Financial Health, Engagement Lift, Card Spend</t>
+  </si>
+  <si>
+    <t>Graduating college</t>
+  </si>
+  <si>
+    <t>Student spending pattern ends, life-stage transition detected</t>
+  </si>
+  <si>
+    <t>Age 22</t>
+  </si>
+  <si>
+    <t>early_career</t>
+  </si>
+  <si>
+    <t>Achievement</t>
+  </si>
+  <si>
+    <t>Tuition payments stop. Student spending fades. A whole new financial chapter begins.</t>
+  </si>
+  <si>
+    <t>Engagement Lift, Financial Health, Primacy, Card Spend</t>
+  </si>
+  <si>
+    <t>Starting a career</t>
+  </si>
+  <si>
+    <t>First payroll deposit detected</t>
   </si>
   <si>
     <t>Age 23</t>
   </si>
   <si>
-    <t>early_career</t>
-  </si>
-  <si>
-    <t>Momentum and Direction</t>
-  </si>
-  <si>
-    <t>Paul starts his early career. BOI Buddy recognizes stable salary and rent patterns and suggests a Mortgage Saver account to convert habit into future home readiness.</t>
-  </si>
-  <si>
-    <t>Balance Growth, Product Sales, Engagement Lift, Financial Health</t>
-  </si>
-  <si>
-    <t>Mature Saving Habits and ISA Recommendation</t>
-  </si>
-  <si>
-    <t>Consistent savings history triggers ISA suitability recommendation</t>
-  </si>
-  <si>
-    <t>Age 30-34</t>
+    <t>A real paycheck arrives. So does the temptation to spend it. MyBank turns the moment into primacy and savings.</t>
+  </si>
+  <si>
+    <t>Balance Growth, Primacy, Financial Health</t>
+  </si>
+  <si>
+    <t>Repaying student debt</t>
+  </si>
+  <si>
+    <t>Loan-servicer payments begin</t>
+  </si>
+  <si>
+    <t>Responsibility</t>
+  </si>
+  <si>
+    <t>The loan servicer's first bill arrives. MyBank turns dread into a clear, manageable plan.</t>
+  </si>
+  <si>
+    <t>Financial Health, Retention, Cost to Serve</t>
+  </si>
+  <si>
+    <t>Gaining financial footing</t>
+  </si>
+  <si>
+    <t>Recurring surplus cash detected</t>
+  </si>
+  <si>
+    <t>Age 24</t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>Cash is finally piling up in checking. MyBank turns idle balance into resilience — automatically.</t>
+  </si>
+  <si>
+    <t>Balance Growth, Financial Health, Engagement Lift</t>
+  </si>
+  <si>
+    <t>Buying a first car</t>
+  </si>
+  <si>
+    <t>Auto-dealer charge and insurance payment detected</t>
+  </si>
+  <si>
+    <t>Age 25</t>
+  </si>
+  <si>
+    <t>young_adult</t>
+  </si>
+  <si>
+    <t>Freedom</t>
+  </si>
+  <si>
+    <t>Alex visits a dealership. MyBank catches the moment of intent — and offers a better loan than the dealer.</t>
+  </si>
+  <si>
+    <t>Credit Growth, Product Sales, Financial Health</t>
+  </si>
+  <si>
+    <t>Tax season</t>
+  </si>
+  <si>
+    <t>€2,400 IRS refund deposit</t>
+  </si>
+  <si>
+    <t>Windfall</t>
+  </si>
+  <si>
+    <t>€2,400 hits Alex's checking. MyBank splits it perfectly between savings, debt, and a little fun.</t>
+  </si>
+  <si>
+    <t>Balance Growth, Financial Health, Product Sales, Card Spend</t>
+  </si>
+  <si>
+    <t>Getting engaged</t>
+  </si>
+  <si>
+    <t>Jewelry merchant purchase €4,800</t>
+  </si>
+  <si>
+    <t>Age 27</t>
+  </si>
+  <si>
+    <t>Love</t>
+  </si>
+  <si>
+    <t>A jewelry purchase signals a life-changing moment. MyBank turns it into a household relationship.</t>
+  </si>
+  <si>
+    <t>Balance Growth, Engagement Lift, Financial Health, Card Spend</t>
+  </si>
+  <si>
+    <t>Becoming a parent</t>
+  </si>
+  <si>
+    <t>Hospital and baby-merchant spend surge</t>
+  </si>
+  <si>
+    <t>Age 30</t>
+  </si>
+  <si>
+    <t>family</t>
+  </si>
+  <si>
+    <t>Joy &amp; Responsibility</t>
+  </si>
+  <si>
+    <t>The hospital bill is just the beginning. MyBank walks the new family through the financial reshaping of parenthood.</t>
+  </si>
+  <si>
+    <t>Engagement Lift, Financial Health, Retention, Balance Growth</t>
+  </si>
+  <si>
+    <t>Dreaming of homeownership</t>
+  </si>
+  <si>
+    <t>Mortgage-rate searches and savings shift</t>
+  </si>
+  <si>
+    <t>Age 32</t>
+  </si>
+  <si>
+    <t>homeowner</t>
+  </si>
+  <si>
+    <t>Ambition</t>
+  </si>
+  <si>
+    <t>Alex starts dreaming of a first home. MyBank turns the dream into a tracked, automated, achievable plan.</t>
+  </si>
+  <si>
+    <t>Balance Growth, Product Sales, Engagement Lift</t>
+  </si>
+  <si>
+    <t>Buying a first home</t>
+  </si>
+  <si>
+    <t>Mortgage funded, fixed costs reset</t>
+  </si>
+  <si>
+    <t>Age 34</t>
+  </si>
+  <si>
+    <t>Closing day. Alex's life — and money — reshape overnight. MyBank is the calm voice through it all.</t>
+  </si>
+  <si>
+    <t>Product Sales, Engagement Lift, Retention, Primacy</t>
+  </si>
+  <si>
+    <t>Renovating the home</t>
+  </si>
+  <si>
+    <t>Hardware and contractor spend pattern detected</t>
+  </si>
+  <si>
+    <t>Age 37</t>
+  </si>
+  <si>
+    <t>Investment</t>
+  </si>
+  <si>
+    <t>Hardware-store charges and contractor payments tell a clear story: Alex is renovating. MyBank offers the right financing at the right time.</t>
+  </si>
+  <si>
+    <t>Product Sales, Credit Growth, Engagement Lift, Card Spend</t>
+  </si>
+  <si>
+    <t>Hitting career peak</t>
+  </si>
+  <si>
+    <t>Payroll up 28%, idle balance growing</t>
+  </si>
+  <si>
+    <t>Age 40</t>
   </si>
   <si>
     <t>midlife</t>
   </si>
   <si>
-    <t>Security and Long-Term Growth</t>
-  </si>
-  <si>
-    <t>By age 30-34, Paul has built consistent savings habits. BOI Buddy recommends an ISA as the next step for tax-efficient long-term growth and life-goal resilience.</t>
-  </si>
-  <si>
-    <t>Wealth Management, Balance Growth, Engagement Lift, Retention</t>
+    <t>Confidence</t>
+  </si>
+  <si>
+    <t>Alex's paycheck is bigger, but cash piles up doing nothing. MyBank turns idle into invested.</t>
+  </si>
+  <si>
+    <t>Balance Growth, Wealth Management, Product Sales, Card Spend</t>
+  </si>
+  <si>
+    <t>Sending a child to college</t>
+  </si>
+  <si>
+    <t>Education-savings shortfall projected</t>
+  </si>
+  <si>
+    <t>Age 45</t>
+  </si>
+  <si>
+    <t>Legacy</t>
+  </si>
+  <si>
+    <t>Alex's child is approaching college. MyBank balances education savings with retirement — without forcing a trade-off.</t>
+  </si>
+  <si>
+    <t>Balance Growth, Engagement Lift, Wealth Management</t>
+  </si>
+  <si>
+    <t>Approaching retirement</t>
+  </si>
+  <si>
+    <t>Projected retirement income below target</t>
+  </si>
+  <si>
+    <t>Age 55</t>
+  </si>
+  <si>
+    <t>pre_retirement</t>
+  </si>
+  <si>
+    <t>Urgency</t>
+  </si>
+  <si>
+    <t>10 years to retirement and the math doesn't add up. MyBank shows it clearly — and offers the path forward.</t>
+  </si>
+  <si>
+    <t>Wealth Management, Financial Health, Balance Growth</t>
+  </si>
+  <si>
+    <t>Entering retirement</t>
+  </si>
+  <si>
+    <t>Payroll stops, Social Security and distributions begin</t>
+  </si>
+  <si>
+    <t>Age 65</t>
+  </si>
+  <si>
+    <t>retirement</t>
+  </si>
+  <si>
+    <t>Payroll stops. New income streams turn on. MyBank is the steady guide through the most-at-risk transition in banking.</t>
+  </si>
+  <si>
+    <t>Retention, Primacy, Wealth Management, Financial Health</t>
+  </si>
+  <si>
+    <t>Planning a legacy</t>
+  </si>
+  <si>
+    <t>Family transfers and estate-attorney payments</t>
+  </si>
+  <si>
+    <t>Age 72</t>
+  </si>
+  <si>
+    <t>legacy</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Alex turns thoughts to family and legacy. MyBank ensures the relationship — and the wealth — pass to the next generation.</t>
+  </si>
+  <si>
+    <t>Wealth Management, Retention, Engagement Lift</t>
   </si>
   <si>
     <t>Lens ID</t>
@@ -284,13 +569,10 @@
     <t>Bank Impact</t>
   </si>
   <si>
-    <t>Day 0</t>
-  </si>
-  <si>
-    <t>€20 parent transfer posted to Smart Start Account</t>
-  </si>
-  <si>
-    <t>Hey Paul! €20 has gone into your account. If you put €5 into your Smart Start Money Pot each week, you could have €100 by your birthday for GAA gear.</t>
+    <t/>
+  </si>
+  <si>
+    <t>New family member detected - child savings account opened</t>
   </si>
   <si>
     <t>in_app</t>
@@ -302,67 +584,52 @@
     <t>personalized_insights</t>
   </si>
   <si>
-    <t>Paul opens the app and checks his sports spend summary.</t>
-  </si>
-  <si>
-    <t>Insight open rate increases and savings intent is created.</t>
-  </si>
-  <si>
-    <t>Day 1</t>
-  </si>
-  <si>
-    <t>Customer taps suggested savings goal</t>
-  </si>
-  <si>
-    <t>BOI Buddy chat: Want me to auto-move €5 every week to your Smart Start Money Pot and track your birthday progress?</t>
-  </si>
-  <si>
-    <t>chatbot</t>
-  </si>
-  <si>
-    <t>Agentic Chat Experience</t>
+    <t>Parents view a projected balance chart for age 18.</t>
+  </si>
+  <si>
+    <t>New deposit relationship established with family</t>
+  </si>
+  <si>
+    <t>Family goal tracking initiated - college fund projection set</t>
+  </si>
+  <si>
+    <t>push</t>
+  </si>
+  <si>
+    <t>Push Notification Experience</t>
   </si>
   <si>
     <t>goals_trackers</t>
   </si>
   <si>
-    <t>Paul confirms automatic weekly transfer.</t>
-  </si>
-  <si>
-    <t>Recurring savings goal activated and tracked in-app.</t>
-  </si>
-  <si>
-    <t>Day 4</t>
-  </si>
-  <si>
-    <t>First weekly transfer completes</t>
-  </si>
-  <si>
-    <t>Great start, Paul. You are 5% of the way to your €100 target. Keep this up and you will hit your birthday goal.</t>
-  </si>
-  <si>
-    <t>push</t>
-  </si>
-  <si>
-    <t>Push Notification Experience</t>
+    <t>Parent taps the push, picks €50/month.</t>
+  </si>
+  <si>
+    <t>Increased account stickiness through goal tracking</t>
+  </si>
+  <si>
+    <t>Recurring deposit pattern detected - monthly transfers starting</t>
+  </si>
+  <si>
+    <t>smart_savings</t>
+  </si>
+  <si>
+    <t>Auto-transfer enabled in two taps.</t>
+  </si>
+  <si>
+    <t>Auto-transfer enabled - recurring deposits active</t>
+  </si>
+  <si>
+    <t>Family engagement signal - goal sharing between parents</t>
   </si>
   <si>
     <t>engagement_builder</t>
   </si>
   <si>
-    <t>Paul keeps the transfer active and checks progress.</t>
-  </si>
-  <si>
-    <t>Goal adherence improves through timely nudges.</t>
-  </si>
-  <si>
-    <t>Day 7</t>
-  </si>
-  <si>
-    <t>Week-one savings streak achieved</t>
-  </si>
-  <si>
-    <t>Email to parent: Paul is on track for his GAA goal. If he maintains this pace, he can unlock points redeemable for vouchers.</t>
+    <t>Parent shares a screenshot to family group chat.</t>
+  </si>
+  <si>
+    <t>Cross-household referral initiated</t>
   </si>
   <si>
     <t>email</t>
@@ -371,19 +638,592 @@
     <t>Email Experience</t>
   </si>
   <si>
-    <t>Parent encourages Paul to continue weekly saving.</t>
-  </si>
-  <si>
-    <t>Family engagement strengthens long-term account retention.</t>
-  </si>
-  <si>
-    <t>Day 14</t>
-  </si>
-  <si>
-    <t>Consistent child savings behavior detected</t>
-  </si>
-  <si>
-    <t>Banker prompt: Offer a quick parent check-in on youth saving habits and reward milestones.</t>
+    <t>Grandparents add €500 birthday gift.</t>
+  </si>
+  <si>
+    <t>First debit card activation - transaction pattern emerging</t>
+  </si>
+  <si>
+    <t>Alex opens the app, smiles at the friendly tone.</t>
+  </si>
+  <si>
+    <t>Youth engagement increased - app usage up 120%</t>
+  </si>
+  <si>
+    <t>Retail spending detected - recurring merchant patterns forming</t>
+  </si>
+  <si>
+    <t>transaction_intelligence</t>
+  </si>
+  <si>
+    <t>Alex explores the category breakdown.</t>
+  </si>
+  <si>
+    <t>Recurring merchant alerts activated</t>
+  </si>
+  <si>
+    <t>Educational spending signal - books and school supplies</t>
+  </si>
+  <si>
+    <t>Alex confirms it, learns to recognize recurring bills.</t>
+  </si>
+  <si>
+    <t>Budget tracking enabled for education category</t>
+  </si>
+  <si>
+    <t>Social spending patterns - entertainment and dining</t>
+  </si>
+  <si>
+    <t>Alex sets a €200 'Headphones' goal.</t>
+  </si>
+  <si>
+    <t>Peer referral initiated</t>
+  </si>
+  <si>
+    <t>Alex shares the story with friends.</t>
+  </si>
+  <si>
+    <t>Tuition payment detected - large education transaction</t>
+  </si>
+  <si>
+    <t>cashflow_forecast</t>
+  </si>
+  <si>
+    <t>Alex sees a 4-month runway projection.</t>
+  </si>
+  <si>
+    <t>Cashflow forecast prevents overdraft - saves €45/month</t>
+  </si>
+  <si>
+    <t>Monthly spending volatility - college living expenses</t>
+  </si>
+  <si>
+    <t>Alex cancels 3 — saves €36/month.</t>
+  </si>
+  <si>
+    <t>Expense management features activated</t>
+  </si>
+  <si>
+    <t>Subscription service accumulation - streaming and apps</t>
+  </si>
+  <si>
+    <t>Alex adjusts spending; avoids overdraft.</t>
+  </si>
+  <si>
+    <t>Subscription optimization - €36 monthly savings identified</t>
+  </si>
+  <si>
+    <t>Travel spending pattern - trips home and campus visits</t>
+  </si>
+  <si>
+    <t>Alex auto-saves €400 on receipt.</t>
+  </si>
+  <si>
+    <t>Parent co-monitoring setup initiated</t>
+  </si>
+  <si>
+    <t>Alex screenshots and texts mom.</t>
+  </si>
+  <si>
+    <t>Credit card application detected - new credit line opened</t>
+  </si>
+  <si>
+    <t>Alex reads the 60-second credit primer.</t>
+  </si>
+  <si>
+    <t>Credit utilization optimization - APR reduced by 3%</t>
+  </si>
+  <si>
+    <t>Payment history pattern emerging - on-time payments starting</t>
+  </si>
+  <si>
+    <t>Alex makes an early €50 payment.</t>
+  </si>
+  <si>
+    <t>Payment reminder engagement increases on-time rate to 98%</t>
+  </si>
+  <si>
+    <t>Credit utilization ratio monitored - 15% average</t>
+  </si>
+  <si>
+    <t>Auto-pay enabled.</t>
+  </si>
+  <si>
+    <t>Credit score improves 32 points in 90 days</t>
+  </si>
+  <si>
+    <t>Credit score improvement trajectory detected</t>
+  </si>
+  <si>
+    <t>Alex feels in control, opens the app daily.</t>
+  </si>
+  <si>
+    <t>Premium card tier becomes eligible</t>
+  </si>
+  <si>
+    <t>offers</t>
+  </si>
+  <si>
+    <t>Alex accepts in one tap.</t>
+  </si>
+  <si>
+    <t>Income deposit detected - first salary received</t>
+  </si>
+  <si>
+    <t>Alex reads the 5-card story.</t>
+  </si>
+  <si>
+    <t>Student loan payoff accelerated by 8 months</t>
+  </si>
+  <si>
+    <t>Student loan payment initiated - repayment plan active</t>
+  </si>
+  <si>
+    <t>Alex bookmarks the checklist.</t>
+  </si>
+  <si>
+    <t>Housing savings goal created - €150K target set</t>
+  </si>
+  <si>
+    <t>Housing search signals - real estate searches and rentals</t>
+  </si>
+  <si>
+    <t>Alex marks the date in calendar.</t>
+  </si>
+  <si>
+    <t>Debt-to-income ratio improves to 22%</t>
+  </si>
+  <si>
+    <t>Lifestyle inflation patterns - spending increases with income</t>
+  </si>
+  <si>
+    <t>direct_deposit_switch</t>
+  </si>
+  <si>
+    <t>Alex starts the switch flow.</t>
+  </si>
+  <si>
+    <t>Financial wellness score increases to 78/100</t>
+  </si>
+  <si>
+    <t>Alex follows the suggested budget.</t>
+  </si>
+  <si>
+    <t>Income stability confirmed - consistent salary deposits</t>
+  </si>
+  <si>
+    <t>Alex starts the one-tap switch.</t>
+  </si>
+  <si>
+    <t>Tax refund optimized - €2,100 additional annual income</t>
+  </si>
+  <si>
+    <t>Tax withholding optimization - W4 adjustment opportunity</t>
+  </si>
+  <si>
+    <t>Alex slows down, opens the spend breakdown.</t>
+  </si>
+  <si>
+    <t>Retirement savings plan recommended - €300/month auto-enrollment</t>
+  </si>
+  <si>
+    <t>Retirement savings signal - 401(k) eligibility reached</t>
+  </si>
+  <si>
+    <t>Alex turns on auto-save.</t>
+  </si>
+  <si>
+    <t>Benefits coverage optimized - 23% cost savings</t>
+  </si>
+  <si>
+    <t>Employee benefits enrollment - health insurance activated</t>
+  </si>
+  <si>
+    <t>Goal accepted; bumps to €75/paycheck.</t>
+  </si>
+  <si>
+    <t>Financial planning session scheduled</t>
+  </si>
+  <si>
+    <t>Alex shares the recap on social.</t>
+  </si>
+  <si>
+    <t>Loan servicer consolidation opportunity detected</t>
+  </si>
+  <si>
+    <t>Alex sees a clear next-month chart.</t>
+  </si>
+  <si>
+    <t>Consolidated loans - APR reduced to 4.2%</t>
+  </si>
+  <si>
+    <t>Interest rate refinance eligible - 1.5% improvement possible</t>
+  </si>
+  <si>
+    <t>Alex transfers in one tap.</t>
+  </si>
+  <si>
+    <t>Payoff timeline accelerated by 4 years</t>
+  </si>
+  <si>
+    <t>Accelerated payoff plan - 5 year vs 10 year scenarios</t>
+  </si>
+  <si>
+    <t>Alex explores the payoff scenarios.</t>
+  </si>
+  <si>
+    <t>Total interest saved - €18,500</t>
+  </si>
+  <si>
+    <t>Forgiveness program qualification evaluated</t>
+  </si>
+  <si>
+    <t>Round-ups enabled.</t>
+  </si>
+  <si>
+    <t>Debt-free milestone achievable by age 30</t>
+  </si>
+  <si>
+    <t>Alex feels momentum, considers refinance later.</t>
+  </si>
+  <si>
+    <t>Emergency fund target reached - 6 months expenses saved</t>
+  </si>
+  <si>
+    <t>Alex taps to learn more.</t>
+  </si>
+  <si>
+    <t>Emergency fund fully funded - financial security improved</t>
+  </si>
+  <si>
+    <t>Investment readiness signal - €50K liquid assets available</t>
+  </si>
+  <si>
+    <t>HYSA opened in the app.</t>
+  </si>
+  <si>
+    <t>Investment account opened - wealth building begins</t>
+  </si>
+  <si>
+    <t>Insurance gap identified - life and disability needs</t>
+  </si>
+  <si>
+    <t>Goal accepted.</t>
+  </si>
+  <si>
+    <t>Insurance protection activated - €500K life coverage</t>
+  </si>
+  <si>
+    <t>Net worth positive milestone achieved - €85K</t>
+  </si>
+  <si>
+    <t>Smart auto-save enabled.</t>
+  </si>
+  <si>
+    <t>Net worth tracking dashboard activated</t>
+  </si>
+  <si>
+    <t>Alex bumps weekly save up.</t>
+  </si>
+  <si>
+    <t>Auto loan application detected - vehicle purchase signals</t>
+  </si>
+  <si>
+    <t>Alex opens the rate offer mid-dealership visit.</t>
+  </si>
+  <si>
+    <t>Auto loan approved at Prime rate - 4.9% APR</t>
+  </si>
+  <si>
+    <t>Insurance quote requested - auto coverage research</t>
+  </si>
+  <si>
+    <t>Alex sees the trade-off chart.</t>
+  </si>
+  <si>
+    <t>Insurance bundled - 18% multi-policy discount</t>
+  </si>
+  <si>
+    <t>Payment capacity confirmed - debt-to-income ratio strong</t>
+  </si>
+  <si>
+    <t>Loan approved at 5.9%.</t>
+  </si>
+  <si>
+    <t>Loan terms optimized - 60 months vs 72 months savings</t>
+  </si>
+  <si>
+    <t>Credit score peak achieved - 752 excellent tier</t>
+  </si>
+  <si>
+    <t>Alex requests a quote.</t>
+  </si>
+  <si>
+    <t>Vehicle coverage and roadside assistance included</t>
+  </si>
+  <si>
+    <t>Alex feels reassured.</t>
+  </si>
+  <si>
+    <t>W2 income maximization opportunity - refund projection €3,200</t>
+  </si>
+  <si>
+    <t>Alex opens the suggestion.</t>
+  </si>
+  <si>
+    <t>Tax refund optimized - €3,200 received within 2 weeks</t>
+  </si>
+  <si>
+    <t>Deduction eligibility evaluated - education and home office</t>
+  </si>
+  <si>
+    <t>Alex accepts with one tap.</t>
+  </si>
+  <si>
+    <t>Deduction strategy implemented - saves €1,800 next year</t>
+  </si>
+  <si>
+    <t>Tax bracket optimization - additional withholding considered</t>
+  </si>
+  <si>
+    <t>Alex sees goal progress jump.</t>
+  </si>
+  <si>
+    <t>Withholding adjusted - monthly cash flow improved</t>
+  </si>
+  <si>
+    <t>Record organization recommendations - digital filing system</t>
+  </si>
+  <si>
+    <t>Alex confirms the payment.</t>
+  </si>
+  <si>
+    <t>Tax organization system adopted</t>
+  </si>
+  <si>
+    <t>Alex feels in control.</t>
+  </si>
+  <si>
+    <t>Joint financial planning initiated - household consolidation</t>
+  </si>
+  <si>
+    <t>Alex laughs, taps yes.</t>
+  </si>
+  <si>
+    <t>Joint account setup - household financial integration</t>
+  </si>
+  <si>
+    <t>Income synchronization detected - dual income optimization</t>
+  </si>
+  <si>
+    <t>Alex and partner accept.</t>
+  </si>
+  <si>
+    <t>Combined credit profile built - mortgage pre-approval</t>
+  </si>
+  <si>
+    <t>Combined debt evaluation - mortgage capacity assessment</t>
+  </si>
+  <si>
+    <t>Partner invited via shared link.</t>
+  </si>
+  <si>
+    <t>Wedding budget tracked - prevents overspending</t>
+  </si>
+  <si>
+    <t>Wedding budget planning signals - expense forecasting</t>
+  </si>
+  <si>
+    <t>Alex enables tagging.</t>
+  </si>
+  <si>
+    <t>Shared financial goals aligned - €80K house fund</t>
+  </si>
+  <si>
+    <t>Alex schedules an in-branch open.</t>
+  </si>
+  <si>
+    <t>Dependent claim eligible - new tax benefits available</t>
+  </si>
+  <si>
+    <t>Alex breathes easier.</t>
+  </si>
+  <si>
+    <t>Tax credits applied - €2,000 annual child tax credit</t>
+  </si>
+  <si>
+    <t>Childcare expense detection - 529 college savings opportunity</t>
+  </si>
+  <si>
+    <t>Account opened.</t>
+  </si>
+  <si>
+    <t>529 plan opened - college fund grows tax-free</t>
+  </si>
+  <si>
+    <t>Insurance needs reassessment - family coverage gap identified</t>
+  </si>
+  <si>
+    <t>Alex follows the runway plan.</t>
+  </si>
+  <si>
+    <t>Life insurance updated - family protection secured</t>
+  </si>
+  <si>
+    <t>Estate planning signal - will and beneficiary review recommended</t>
+  </si>
+  <si>
+    <t>Alex follows the suggestions.</t>
+  </si>
+  <si>
+    <t>Estate documents created - peace of mind established</t>
+  </si>
+  <si>
+    <t>Alex shares the recap.</t>
+  </si>
+  <si>
+    <t>Mortgage readiness assessment - down payment progress tracked</t>
+  </si>
+  <si>
+    <t>Alex opens the planner.</t>
+  </si>
+  <si>
+    <t>Down payment goal achieved - 20% saved (€60K)</t>
+  </si>
+  <si>
+    <t>Credit score optimization - 780+ required for best rates</t>
+  </si>
+  <si>
+    <t>Credit optimized - mortgage rate locked at 4.2%</t>
+  </si>
+  <si>
+    <t>Debt-to-income improvement - mortgage capacity grows</t>
+  </si>
+  <si>
+    <t>Auto-save enabled.</t>
+  </si>
+  <si>
+    <t>First-time buyer program identified - €15K incentive</t>
+  </si>
+  <si>
+    <t>Home affordability analysis - price range recommendation</t>
+  </si>
+  <si>
+    <t>Alex confirms the boost.</t>
+  </si>
+  <si>
+    <t>Home purchase pre-approval completed</t>
+  </si>
+  <si>
+    <t>Alex feels confident, stays the course.</t>
+  </si>
+  <si>
+    <t>Mortgage application submitted - underwriting in progress</t>
+  </si>
+  <si>
+    <t>Alex follows the 5-card homeowner story.</t>
+  </si>
+  <si>
+    <t>Mortgage funded - €300K loan at 4.2% APR</t>
+  </si>
+  <si>
+    <t>Closing date scheduled - 45 days to completion</t>
+  </si>
+  <si>
+    <t>Alex accepts the new budget.</t>
+  </si>
+  <si>
+    <t>Home insurance secured - €1,200/year bundled rate</t>
+  </si>
+  <si>
+    <t>Home insurance quotes received - coverage options compared</t>
+  </si>
+  <si>
+    <t>Auto-save scheduled.</t>
+  </si>
+  <si>
+    <t>Homeownership begins - asset building accelerates</t>
+  </si>
+  <si>
+    <t>Property tax and HOA analysis completed</t>
+  </si>
+  <si>
+    <t>Alex switches.</t>
+  </si>
+  <si>
+    <t>Wealth trajectory improves - real estate equity grows</t>
+  </si>
+  <si>
+    <t>Alex feels capable.</t>
+  </si>
+  <si>
+    <t>Home improvement spending detected - construction loans available</t>
+  </si>
+  <si>
+    <t>Alex taps to see options.</t>
+  </si>
+  <si>
+    <t>Home equity line available - €80K HELOC established</t>
+  </si>
+  <si>
+    <t>Equity buildup signals - refinance opportunity evaluated</t>
+  </si>
+  <si>
+    <t>Alex compares the math.</t>
+  </si>
+  <si>
+    <t>Renovation funded - home value increases 12%</t>
+  </si>
+  <si>
+    <t>Property value appreciation - appraisal increases by 8%</t>
+  </si>
+  <si>
+    <t>HELOC approved at €50K line.</t>
+  </si>
+  <si>
+    <t>Refinance completed - rate improved to 3.8%</t>
+  </si>
+  <si>
+    <t>Tax deduction analysis - home office and improvements</t>
+  </si>
+  <si>
+    <t>Balance moved.</t>
+  </si>
+  <si>
+    <t>Net worth increased by €75K from equity gains</t>
+  </si>
+  <si>
+    <t>Alex uses tracker daily.</t>
+  </si>
+  <si>
+    <t>High income phase detected - €250K+ annual earnings</t>
+  </si>
+  <si>
+    <t>Alex opens the recommendation.</t>
+  </si>
+  <si>
+    <t>Tax-efficient investment strategy implemented</t>
+  </si>
+  <si>
+    <t>Investment capacity maximized - €30K+ annual contributions</t>
+  </si>
+  <si>
+    <t>Sweep accepted.</t>
+  </si>
+  <si>
+    <t>Wealth management advisor engagement recommended</t>
+  </si>
+  <si>
+    <t>Tax optimization critical - wealth preservation strategies</t>
+  </si>
+  <si>
+    <t>Alex requests info.</t>
+  </si>
+  <si>
+    <t>Executive compensation optimized - €45K additional after-tax</t>
+  </si>
+  <si>
+    <t>Executive benefits available - stock options and deferred comp</t>
   </si>
   <si>
     <t>banker</t>
@@ -392,217 +1232,163 @@
     <t>Banker CRM Experience</t>
   </si>
   <si>
-    <t>Parent accepts short guidance call.</t>
-  </si>
-  <si>
-    <t>Higher confidence in BOI advice and deeper relationship value.</t>
-  </si>
-  <si>
-    <t>Eligibility trigger for Student Account</t>
-  </si>
-  <si>
-    <t>You are ready for a Student Account, Paul. It is designed for your next stage and works with your current savings habits.</t>
-  </si>
-  <si>
-    <t>Paul reviews benefits and taps to continue.</t>
-  </si>
-  <si>
-    <t>Seamless product migration with no attrition.</t>
-  </si>
-  <si>
-    <t>Customer opens transition flow</t>
-  </si>
-  <si>
-    <t>BOI Buddy chat: Based on your saving pattern, start a light monthly budget and split it into Driving Lessons and College Fees goals.</t>
-  </si>
-  <si>
-    <t>Paul chooses a starter budget and activates both goals.</t>
-  </si>
-  <si>
-    <t>Goal adoption increases financial planning behavior.</t>
-  </si>
-  <si>
-    <t>Day 3</t>
-  </si>
-  <si>
-    <t>First week spending remains inside target</t>
-  </si>
-  <si>
-    <t>Nice work. You are on budget this week and still contributing to both goals.</t>
-  </si>
-  <si>
-    <t>Paul keeps weekly spending limits active.</t>
-  </si>
-  <si>
-    <t>Improved budget consistency and app stickiness.</t>
-  </si>
-  <si>
-    <t>Seven-day budget and goal data available</t>
-  </si>
-  <si>
-    <t>Email: Your weekly budget snapshot is ready. You are pacing well for driving lessons and college fee targets.</t>
-  </si>
-  <si>
-    <t>cashflow_forecast</t>
-  </si>
-  <si>
-    <t>Paul and parent review progress together.</t>
-  </si>
-  <si>
-    <t>Higher transparency and confidence in BOI guidance.</t>
-  </si>
-  <si>
-    <t>Strong early student budgeting behavior</t>
-  </si>
-  <si>
-    <t>Banker task: Offer a short check-in to optimize goal allocation between near-term driving costs and college timeline.</t>
-  </si>
-  <si>
-    <t>Paul accepts a 15-minute planning call.</t>
-  </si>
-  <si>
-    <t>Retention and primacy strengthened before adulthood account competition.</t>
-  </si>
-  <si>
-    <t>Salary in and rent out pattern stabilizes over 3 months</t>
-  </si>
-  <si>
-    <t>You now have a reliable monthly surplus after rent. You are in a strong position to start a Mortgage Saver account.</t>
-  </si>
-  <si>
-    <t>Paul reviews projected 12-month surplus.</t>
-  </si>
-  <si>
-    <t>Mortgage saver intent captured in-app.</t>
-  </si>
-  <si>
-    <t>Customer requests next-step guidance</t>
-  </si>
-  <si>
-    <t>BOI Buddy chat: Set a Home Deposit goal now. I can recommend an amount that still keeps your rent-month buffer safe.</t>
-  </si>
-  <si>
-    <t>Paul accepts a monthly deposit target.</t>
-  </si>
-  <si>
-    <t>Home deposit goal launched with realistic contribution schedule.</t>
-  </si>
-  <si>
-    <t>Day 5</t>
-  </si>
-  <si>
-    <t>First salary cycle after recommendation</t>
-  </si>
-  <si>
-    <t>We can auto-move your savings the day after salary to reduce friction and protect consistency.</t>
-  </si>
-  <si>
-    <t>smart_savings</t>
-  </si>
-  <si>
-    <t>Paul enables salary-linked transfer automation.</t>
-  </si>
-  <si>
-    <t>Consistent monthly savings inflow established.</t>
-  </si>
-  <si>
-    <t>Day 8</t>
-  </si>
-  <si>
-    <t>First transfer completed</t>
-  </si>
-  <si>
-    <t>Email: Great start. At your current pace, your projected home deposit in 24 months is clearly on track.</t>
-  </si>
-  <si>
-    <t>Paul keeps contribution level unchanged.</t>
-  </si>
-  <si>
-    <t>Confidence in plan increases persistence.</t>
-  </si>
-  <si>
-    <t>Day 21</t>
-  </si>
-  <si>
-    <t>Three-week consistency milestone</t>
-  </si>
-  <si>
-    <t>Banker prompt: Offer a pre-mortgage readiness review and explain documentation timeline early.</t>
-  </si>
-  <si>
-    <t>Paul books a branch consultation.</t>
-  </si>
-  <si>
-    <t>Higher probability of BOI mortgage origination.</t>
-  </si>
-  <si>
-    <t>Savings consistency and balance growth cross recommendation threshold</t>
-  </si>
-  <si>
-    <t>You have built excellent savings discipline. An ISA could help your money work harder while supporting long-term goals.</t>
-  </si>
-  <si>
-    <t>Paul explores ISA explainer content.</t>
-  </si>
-  <si>
-    <t>High-intent wealth journey begins.</t>
-  </si>
-  <si>
-    <t>Customer enters investment planning flow</t>
-  </si>
-  <si>
-    <t>BOI Buddy chat: Let us map your goals (family security, dream home upgrades, education support) to an ISA contribution plan.</t>
-  </si>
-  <si>
-    <t>Paul sets goal-linked ISA contribution levels.</t>
-  </si>
-  <si>
-    <t>Personetics goals tools directly tied to wealth product adoption.</t>
-  </si>
-  <si>
-    <t>Day 6</t>
-  </si>
-  <si>
-    <t>Scheduled ISA contribution date</t>
-  </si>
-  <si>
-    <t>Quick reminder: your monthly ISA contribution is due tomorrow. Keeping consistency protects your long-term plan.</t>
-  </si>
-  <si>
-    <t>Paul confirms contribution.</t>
-  </si>
-  <si>
-    <t>Sustained contribution behavior maintained.</t>
-  </si>
-  <si>
-    <t>Day 10</t>
-  </si>
-  <si>
-    <t>First ISA contribution posted</t>
-  </si>
-  <si>
-    <t>Email: Your ISA is active. Here is your contribution summary and long-term projection by each life goal.</t>
-  </si>
-  <si>
-    <t>Paul shares summary with partner.</t>
-  </si>
-  <si>
-    <t>Household confidence supports retention and wallet share.</t>
-  </si>
-  <si>
-    <t>Day 20</t>
-  </si>
-  <si>
-    <t>Customer demonstrates steady ISA behavior</t>
-  </si>
-  <si>
-    <t>Banker task: Offer annual ISA optimization review and align contributions with upcoming family milestones.</t>
-  </si>
-  <si>
-    <t>Paul books annual review.</t>
-  </si>
-  <si>
-    <t>Long-term wealth relationship deepened.</t>
+    <t>Alex books a call.</t>
+  </si>
+  <si>
+    <t>Generational wealth building initiated</t>
+  </si>
+  <si>
+    <t>Rollover initiated.</t>
+  </si>
+  <si>
+    <t>529 plan maturation - college funding distributions begin</t>
+  </si>
+  <si>
+    <t>529 distributions deployed - €80K college funding released</t>
+  </si>
+  <si>
+    <t>Parent Plus loan eligibility evaluated - funding gap analysis</t>
+  </si>
+  <si>
+    <t>529 opened.</t>
+  </si>
+  <si>
+    <t>Family financial aid optimized - €18K in aid identified</t>
+  </si>
+  <si>
+    <t>Scholarship optimization - financial aid packaging reviewed</t>
+  </si>
+  <si>
+    <t>Split accepted.</t>
+  </si>
+  <si>
+    <t>College costs managed - 4-year plan projected and funded</t>
+  </si>
+  <si>
+    <t>College savings strategy transition - spending phase begins</t>
+  </si>
+  <si>
+    <t>Invites sent.</t>
+  </si>
+  <si>
+    <t>Education expense tax benefits maximized</t>
+  </si>
+  <si>
+    <t>Alex makes it the family meeting tool.</t>
+  </si>
+  <si>
+    <t>Retirement readiness assessment - 10 year countdown activated</t>
+  </si>
+  <si>
+    <t>Alex absorbs the number.</t>
+  </si>
+  <si>
+    <t>Retirement projection updated - €2.5M portfolio sufficient</t>
+  </si>
+  <si>
+    <t>Portfolio rebalancing signals - risk reduction strategy</t>
+  </si>
+  <si>
+    <t>Activated.</t>
+  </si>
+  <si>
+    <t>Asset allocation adjusted - 50% equities, 50% bonds</t>
+  </si>
+  <si>
+    <t>Social Security timing analysis - claiming strategy evaluated</t>
+  </si>
+  <si>
+    <t>Alex schedules the redirect.</t>
+  </si>
+  <si>
+    <t>Social Security claiming optimized - €42K annual benefit</t>
+  </si>
+  <si>
+    <t>Healthcare cost planning - Medicare and insurance gaps</t>
+  </si>
+  <si>
+    <t>Books a session.</t>
+  </si>
+  <si>
+    <t>Retirement lifestyle planning completed</t>
+  </si>
+  <si>
+    <t>Alex feels back in control.</t>
+  </si>
+  <si>
+    <t>Retirement date reached - income transition activated</t>
+  </si>
+  <si>
+    <t>Alex follows the new cash-flow story.</t>
+  </si>
+  <si>
+    <t>Retirement income established - €180K annual cash flow</t>
+  </si>
+  <si>
+    <t>Pension and Social Security claims processed</t>
+  </si>
+  <si>
+    <t>Advisor session booked.</t>
+  </si>
+  <si>
+    <t>Tax burden reduced - 22% effective tax rate</t>
+  </si>
+  <si>
+    <t>Distribution strategy optimized - tax-efficient withdrawals</t>
+  </si>
+  <si>
+    <t>Alex feels secure.</t>
+  </si>
+  <si>
+    <t>Healthcare costs secured - Medicare and supplemental coverage</t>
+  </si>
+  <si>
+    <t>Legacy planning prioritized - wealth transfer preparation</t>
+  </si>
+  <si>
+    <t>Alex schedules planning call.</t>
+  </si>
+  <si>
+    <t>Retirement lifestyle sustainable - 30+ year projection</t>
+  </si>
+  <si>
+    <t>Alex stays loyal.</t>
+  </si>
+  <si>
+    <t>Estate planning finalized - will and trusts established</t>
+  </si>
+  <si>
+    <t>Estate plan reduces taxes by €350K</t>
+  </si>
+  <si>
+    <t>Charitable giving goals identified - impact strategy</t>
+  </si>
+  <si>
+    <t>Tracker enabled.</t>
+  </si>
+  <si>
+    <t>Charitable foundation established - €2M endowment</t>
+  </si>
+  <si>
+    <t>Family wealth transfer planning - multigenerational strategy</t>
+  </si>
+  <si>
+    <t>Calls scheduled.</t>
+  </si>
+  <si>
+    <t>Family wealth transfer secured - tax-efficient distribution</t>
+  </si>
+  <si>
+    <t>Life insurance portfolio optimization - legacy funding</t>
+  </si>
+  <si>
+    <t>DAF opened.</t>
+  </si>
+  <si>
+    <t>Generational legacy built - impact defined for 3 generations</t>
+  </si>
+  <si>
+    <t>Family accounts linked.</t>
   </si>
   <si>
     <t>Financial Signals</t>
@@ -611,70 +1397,10 @@
     <t>MyBank Capabilities</t>
   </si>
   <si>
-    <t xml:space="preserve">Regular parent-funded deposits
-Card spend concentrated in sports merchants
-Savings opportunity from predictable weekly inflows</t>
-  </si>
-  <si>
-    <t>transaction_intelligence, goals_trackers, smart_savings, engagement_builder, gen_ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Healthy savings streak
-Increasing education-related spend
-Predictable monthly inflows with low volatility</t>
-  </si>
-  <si>
-    <t>transaction_intelligence, cashflow_forecast, goals_trackers, engagement_builder, gen_ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stable payroll credit
-Recurring rent debit
-Positive monthly surplus</t>
-  </si>
-  <si>
-    <t>cashflow_forecast, smart_savings, goals_trackers, engagement_builder, gen_ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Savings contributions sustained over time
-Low missed transfer rate
-Growing average balances</t>
-  </si>
-  <si>
-    <t>personalized_insights, goals_trackers, smart_savings, engagement_builder, gen_ai</t>
-  </si>
-  <si>
     <t>Bank Story</t>
   </si>
   <si>
     <t>Business Impact Metrics</t>
-  </si>
-  <si>
-    <t>BOI Buddy builds trust early by linking real transactions to a simple goal and reward journey.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Youth savings balances (increase: +12%)
-Family digital engagement (increase: +18%)</t>
-  </si>
-  <si>
-    <t>BOI Buddy keeps Paul in BOI's ecosystem by making the student transition proactive, personal, and low-friction.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student account conversion (increase: +20%)
-Youth retention (increase: +14%)</t>
-  </si>
-  <si>
-    <t>BOI Buddy turns transactional data into a mortgage pipeline early, increasing future lending conversion.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mortgage saver openings (increase: +17%)
-Future mortgage conversion (increase: +9%)</t>
-  </si>
-  <si>
-    <t>BOI Buddy remains Paul's life stage companion by evolving recommendations from saving to wealth-building.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ISA conversion (increase: +11%)
-Affluent customer retention (increase: +8%)</t>
   </si>
 </sst>
 </file>
@@ -1098,7 +1824,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1152,22 +1878,22 @@
         <v>10</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>12</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>13</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>14</v>
-      </c>
-      <c r="I2" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -1175,28 +1901,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
         <v>17</v>
       </c>
-      <c r="D3">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" t="s">
         <v>18</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
         <v>19</v>
       </c>
-      <c r="G3" t="s">
+      <c r="I3" t="s">
         <v>20</v>
-      </c>
-      <c r="H3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -1204,28 +1930,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
         <v>23</v>
       </c>
-      <c r="C4" t="s">
+      <c r="F4" t="s">
         <v>24</v>
       </c>
-      <c r="D4">
-        <v>23</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="G4" t="s">
         <v>25</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H4" t="s">
         <v>26</v>
       </c>
-      <c r="G4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" t="s">
-        <v>28</v>
-      </c>
       <c r="I4" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -1233,28 +1959,492 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5">
+        <v>19</v>
+      </c>
+      <c r="E5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" t="s">
         <v>30</v>
       </c>
-      <c r="C5" t="s">
+      <c r="H5" t="s">
         <v>31</v>
       </c>
-      <c r="D5">
+      <c r="I5" t="s">
         <v>32</v>
       </c>
-      <c r="E5" t="s">
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6">
+        <v>22</v>
+      </c>
+      <c r="E6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7">
+        <v>23</v>
+      </c>
+      <c r="E7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" t="s">
+        <v>43</v>
+      </c>
+      <c r="I7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8">
+        <v>23</v>
+      </c>
+      <c r="E8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" t="s">
+        <v>48</v>
+      </c>
+      <c r="I8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9">
+        <v>24</v>
+      </c>
+      <c r="E9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H9" t="s">
+        <v>54</v>
+      </c>
+      <c r="I9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10">
+        <v>25</v>
+      </c>
+      <c r="E10" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10" t="s">
+        <v>60</v>
+      </c>
+      <c r="H10" t="s">
+        <v>61</v>
+      </c>
+      <c r="I10" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11">
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>58</v>
+      </c>
+      <c r="F11" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" t="s">
+        <v>65</v>
+      </c>
+      <c r="H11" t="s">
+        <v>66</v>
+      </c>
+      <c r="I11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D12">
+        <v>27</v>
+      </c>
+      <c r="E12" t="s">
+        <v>70</v>
+      </c>
+      <c r="F12" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12" t="s">
+        <v>71</v>
+      </c>
+      <c r="H12" t="s">
+        <v>72</v>
+      </c>
+      <c r="I12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>74</v>
+      </c>
+      <c r="C13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13">
+        <v>30</v>
+      </c>
+      <c r="E13" t="s">
+        <v>76</v>
+      </c>
+      <c r="F13" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13" t="s">
+        <v>78</v>
+      </c>
+      <c r="H13" t="s">
+        <v>79</v>
+      </c>
+      <c r="I13" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C14" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14">
         <v>32</v>
       </c>
-      <c r="F5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="E14" t="s">
+        <v>83</v>
+      </c>
+      <c r="F14" t="s">
+        <v>84</v>
+      </c>
+      <c r="G14" t="s">
+        <v>85</v>
+      </c>
+      <c r="H14" t="s">
+        <v>86</v>
+      </c>
+      <c r="I14" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" t="s">
+        <v>89</v>
+      </c>
+      <c r="D15">
         <v>34</v>
       </c>
-      <c r="H5" t="s">
-        <v>35</v>
-      </c>
-      <c r="I5" t="s">
-        <v>36</v>
+      <c r="E15" t="s">
+        <v>90</v>
+      </c>
+      <c r="F15" t="s">
+        <v>84</v>
+      </c>
+      <c r="G15" t="s">
+        <v>37</v>
+      </c>
+      <c r="H15" t="s">
+        <v>91</v>
+      </c>
+      <c r="I15" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16">
+        <v>37</v>
+      </c>
+      <c r="E16" t="s">
+        <v>95</v>
+      </c>
+      <c r="F16" t="s">
+        <v>84</v>
+      </c>
+      <c r="G16" t="s">
+        <v>96</v>
+      </c>
+      <c r="H16" t="s">
+        <v>97</v>
+      </c>
+      <c r="I16" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>99</v>
+      </c>
+      <c r="C17" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17">
+        <v>40</v>
+      </c>
+      <c r="E17" t="s">
+        <v>101</v>
+      </c>
+      <c r="F17" t="s">
+        <v>102</v>
+      </c>
+      <c r="G17" t="s">
+        <v>103</v>
+      </c>
+      <c r="H17" t="s">
+        <v>104</v>
+      </c>
+      <c r="I17" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>106</v>
+      </c>
+      <c r="C18" t="s">
+        <v>107</v>
+      </c>
+      <c r="D18">
+        <v>45</v>
+      </c>
+      <c r="E18" t="s">
+        <v>108</v>
+      </c>
+      <c r="F18" t="s">
+        <v>102</v>
+      </c>
+      <c r="G18" t="s">
+        <v>109</v>
+      </c>
+      <c r="H18" t="s">
+        <v>110</v>
+      </c>
+      <c r="I18" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C19" t="s">
+        <v>113</v>
+      </c>
+      <c r="D19">
+        <v>55</v>
+      </c>
+      <c r="E19" t="s">
+        <v>114</v>
+      </c>
+      <c r="F19" t="s">
+        <v>115</v>
+      </c>
+      <c r="G19" t="s">
+        <v>116</v>
+      </c>
+      <c r="H19" t="s">
+        <v>117</v>
+      </c>
+      <c r="I19" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>119</v>
+      </c>
+      <c r="C20" t="s">
+        <v>120</v>
+      </c>
+      <c r="D20">
+        <v>65</v>
+      </c>
+      <c r="E20" t="s">
+        <v>121</v>
+      </c>
+      <c r="F20" t="s">
+        <v>122</v>
+      </c>
+      <c r="G20" t="s">
+        <v>60</v>
+      </c>
+      <c r="H20" t="s">
+        <v>123</v>
+      </c>
+      <c r="I20" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>125</v>
+      </c>
+      <c r="C21" t="s">
+        <v>126</v>
+      </c>
+      <c r="D21">
+        <v>72</v>
+      </c>
+      <c r="E21" t="s">
+        <v>127</v>
+      </c>
+      <c r="F21" t="s">
+        <v>128</v>
+      </c>
+      <c r="G21" t="s">
+        <v>129</v>
+      </c>
+      <c r="H21" t="s">
+        <v>130</v>
+      </c>
+      <c r="I21" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -1276,156 +2466,156 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>37</v>
+        <v>132</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>38</v>
+        <v>133</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>39</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>135</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>136</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>137</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>139</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>140</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>141</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>48</v>
+        <v>143</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>144</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>145</v>
       </c>
       <c r="D4" t="s">
-        <v>51</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>147</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>151</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>152</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>153</v>
       </c>
       <c r="D6" t="s">
-        <v>59</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>60</v>
+        <v>155</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>156</v>
       </c>
       <c r="C7" t="s">
-        <v>62</v>
+        <v>157</v>
       </c>
       <c r="D7" t="s">
-        <v>63</v>
+        <v>158</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>64</v>
+        <v>159</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="D8" t="s">
-        <v>67</v>
+        <v>162</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>68</v>
+        <v>163</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>164</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>165</v>
       </c>
       <c r="D9" t="s">
-        <v>71</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>72</v>
+        <v>167</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>168</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>169</v>
       </c>
       <c r="D10" t="s">
-        <v>75</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>76</v>
+        <v>171</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>172</v>
       </c>
       <c r="C11" t="s">
-        <v>78</v>
+        <v>173</v>
       </c>
       <c r="D11" t="s">
-        <v>79</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -1436,7 +2626,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K101"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1458,31 +2648,31 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>80</v>
+        <v>175</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>81</v>
+        <v>176</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>83</v>
+        <v>178</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>84</v>
+        <v>179</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>86</v>
+        <v>181</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>87</v>
+        <v>182</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>88</v>
+        <v>183</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -1496,28 +2686,28 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>184</v>
       </c>
       <c r="E2" t="s">
-        <v>90</v>
+        <v>185</v>
       </c>
       <c r="F2" t="s">
-        <v>91</v>
+        <v>184</v>
       </c>
       <c r="G2" t="s">
-        <v>92</v>
+        <v>186</v>
       </c>
       <c r="H2" t="s">
-        <v>93</v>
+        <v>187</v>
       </c>
       <c r="I2" t="s">
-        <v>94</v>
+        <v>188</v>
       </c>
       <c r="J2" t="s">
-        <v>95</v>
+        <v>189</v>
       </c>
       <c r="K2" t="s">
-        <v>96</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -1531,28 +2721,28 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>184</v>
       </c>
       <c r="E3" t="s">
-        <v>98</v>
+        <v>191</v>
       </c>
       <c r="F3" t="s">
-        <v>99</v>
+        <v>184</v>
       </c>
       <c r="G3" t="s">
-        <v>100</v>
+        <v>192</v>
       </c>
       <c r="H3" t="s">
-        <v>101</v>
+        <v>193</v>
       </c>
       <c r="I3" t="s">
-        <v>102</v>
+        <v>194</v>
       </c>
       <c r="J3" t="s">
-        <v>103</v>
+        <v>195</v>
       </c>
       <c r="K3" t="s">
-        <v>104</v>
+        <v>196</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -1566,28 +2756,28 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>105</v>
+        <v>184</v>
       </c>
       <c r="E4" t="s">
-        <v>106</v>
+        <v>197</v>
       </c>
       <c r="F4" t="s">
-        <v>107</v>
+        <v>184</v>
       </c>
       <c r="G4" t="s">
-        <v>108</v>
+        <v>186</v>
       </c>
       <c r="H4" t="s">
-        <v>109</v>
+        <v>187</v>
       </c>
       <c r="I4" t="s">
-        <v>110</v>
+        <v>198</v>
       </c>
       <c r="J4" t="s">
-        <v>111</v>
+        <v>199</v>
       </c>
       <c r="K4" t="s">
-        <v>112</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -1601,28 +2791,28 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>113</v>
+        <v>184</v>
       </c>
       <c r="E5" t="s">
-        <v>114</v>
+        <v>201</v>
       </c>
       <c r="F5" t="s">
-        <v>115</v>
+        <v>184</v>
       </c>
       <c r="G5" t="s">
-        <v>116</v>
+        <v>192</v>
       </c>
       <c r="H5" t="s">
-        <v>117</v>
+        <v>193</v>
       </c>
       <c r="I5" t="s">
-        <v>110</v>
+        <v>202</v>
       </c>
       <c r="J5" t="s">
-        <v>118</v>
+        <v>203</v>
       </c>
       <c r="K5" t="s">
-        <v>119</v>
+        <v>204</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -1636,28 +2826,28 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>120</v>
+        <v>184</v>
       </c>
       <c r="E6" t="s">
-        <v>121</v>
+        <v>185</v>
       </c>
       <c r="F6" t="s">
-        <v>122</v>
+        <v>184</v>
       </c>
       <c r="G6" t="s">
-        <v>123</v>
+        <v>205</v>
       </c>
       <c r="H6" t="s">
-        <v>124</v>
+        <v>206</v>
       </c>
       <c r="I6" t="s">
-        <v>94</v>
+        <v>202</v>
       </c>
       <c r="J6" t="s">
-        <v>125</v>
+        <v>207</v>
       </c>
       <c r="K6" t="s">
-        <v>126</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -1665,34 +2855,34 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>89</v>
+        <v>184</v>
       </c>
       <c r="E7" t="s">
-        <v>127</v>
+        <v>208</v>
       </c>
       <c r="F7" t="s">
-        <v>128</v>
+        <v>184</v>
       </c>
       <c r="G7" t="s">
-        <v>92</v>
+        <v>192</v>
       </c>
       <c r="H7" t="s">
-        <v>93</v>
+        <v>193</v>
       </c>
       <c r="I7" t="s">
-        <v>94</v>
+        <v>202</v>
       </c>
       <c r="J7" t="s">
-        <v>129</v>
+        <v>209</v>
       </c>
       <c r="K7" t="s">
-        <v>130</v>
+        <v>210</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -1700,34 +2890,34 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C8">
         <v>2</v>
       </c>
       <c r="D8" t="s">
-        <v>97</v>
+        <v>184</v>
       </c>
       <c r="E8" t="s">
-        <v>131</v>
+        <v>211</v>
       </c>
       <c r="F8" t="s">
-        <v>132</v>
+        <v>184</v>
       </c>
       <c r="G8" t="s">
-        <v>100</v>
+        <v>186</v>
       </c>
       <c r="H8" t="s">
-        <v>101</v>
+        <v>187</v>
       </c>
       <c r="I8" t="s">
-        <v>102</v>
+        <v>212</v>
       </c>
       <c r="J8" t="s">
-        <v>133</v>
+        <v>213</v>
       </c>
       <c r="K8" t="s">
-        <v>134</v>
+        <v>214</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -1735,34 +2925,34 @@
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C9">
         <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>135</v>
+        <v>184</v>
       </c>
       <c r="E9" t="s">
-        <v>136</v>
+        <v>215</v>
       </c>
       <c r="F9" t="s">
-        <v>137</v>
+        <v>184</v>
       </c>
       <c r="G9" t="s">
-        <v>108</v>
+        <v>192</v>
       </c>
       <c r="H9" t="s">
-        <v>109</v>
+        <v>193</v>
       </c>
       <c r="I9" t="s">
-        <v>110</v>
+        <v>212</v>
       </c>
       <c r="J9" t="s">
-        <v>138</v>
+        <v>216</v>
       </c>
       <c r="K9" t="s">
-        <v>139</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -1770,34 +2960,34 @@
         <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10">
         <v>4</v>
       </c>
       <c r="D10" t="s">
-        <v>113</v>
+        <v>184</v>
       </c>
       <c r="E10" t="s">
-        <v>140</v>
+        <v>218</v>
       </c>
       <c r="F10" t="s">
-        <v>141</v>
+        <v>184</v>
       </c>
       <c r="G10" t="s">
-        <v>116</v>
+        <v>186</v>
       </c>
       <c r="H10" t="s">
-        <v>117</v>
+        <v>187</v>
       </c>
       <c r="I10" t="s">
-        <v>142</v>
+        <v>194</v>
       </c>
       <c r="J10" t="s">
-        <v>143</v>
+        <v>219</v>
       </c>
       <c r="K10" t="s">
-        <v>144</v>
+        <v>220</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -1805,34 +2995,34 @@
         <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C11">
         <v>5</v>
       </c>
       <c r="D11" t="s">
-        <v>120</v>
+        <v>184</v>
       </c>
       <c r="E11" t="s">
-        <v>145</v>
+        <v>208</v>
       </c>
       <c r="F11" t="s">
-        <v>146</v>
+        <v>184</v>
       </c>
       <c r="G11" t="s">
-        <v>123</v>
+        <v>186</v>
       </c>
       <c r="H11" t="s">
-        <v>124</v>
+        <v>187</v>
       </c>
       <c r="I11" t="s">
-        <v>94</v>
+        <v>202</v>
       </c>
       <c r="J11" t="s">
-        <v>147</v>
+        <v>221</v>
       </c>
       <c r="K11" t="s">
-        <v>148</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -1840,34 +3030,34 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>89</v>
+        <v>184</v>
       </c>
       <c r="E12" t="s">
-        <v>149</v>
+        <v>222</v>
       </c>
       <c r="F12" t="s">
-        <v>150</v>
+        <v>184</v>
       </c>
       <c r="G12" t="s">
-        <v>92</v>
+        <v>186</v>
       </c>
       <c r="H12" t="s">
-        <v>93</v>
+        <v>187</v>
       </c>
       <c r="I12" t="s">
-        <v>142</v>
+        <v>223</v>
       </c>
       <c r="J12" t="s">
-        <v>151</v>
+        <v>224</v>
       </c>
       <c r="K12" t="s">
-        <v>152</v>
+        <v>225</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1875,34 +3065,34 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C13">
         <v>2</v>
       </c>
       <c r="D13" t="s">
-        <v>97</v>
+        <v>184</v>
       </c>
       <c r="E13" t="s">
-        <v>153</v>
+        <v>226</v>
       </c>
       <c r="F13" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="G13" t="s">
-        <v>100</v>
+        <v>192</v>
       </c>
       <c r="H13" t="s">
-        <v>101</v>
+        <v>193</v>
       </c>
       <c r="I13" t="s">
-        <v>102</v>
+        <v>212</v>
       </c>
       <c r="J13" t="s">
-        <v>155</v>
+        <v>227</v>
       </c>
       <c r="K13" t="s">
-        <v>156</v>
+        <v>228</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1910,34 +3100,34 @@
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C14">
         <v>3</v>
       </c>
       <c r="D14" t="s">
-        <v>157</v>
+        <v>184</v>
       </c>
       <c r="E14" t="s">
-        <v>158</v>
+        <v>229</v>
       </c>
       <c r="F14" t="s">
-        <v>159</v>
+        <v>184</v>
       </c>
       <c r="G14" t="s">
-        <v>108</v>
+        <v>192</v>
       </c>
       <c r="H14" t="s">
-        <v>109</v>
+        <v>193</v>
       </c>
       <c r="I14" t="s">
-        <v>160</v>
+        <v>223</v>
       </c>
       <c r="J14" t="s">
-        <v>161</v>
+        <v>230</v>
       </c>
       <c r="K14" t="s">
-        <v>162</v>
+        <v>231</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1945,34 +3135,34 @@
         <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C15">
         <v>4</v>
       </c>
       <c r="D15" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="E15" t="s">
-        <v>164</v>
+        <v>232</v>
       </c>
       <c r="F15" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="G15" t="s">
-        <v>116</v>
+        <v>186</v>
       </c>
       <c r="H15" t="s">
-        <v>117</v>
+        <v>187</v>
       </c>
       <c r="I15" t="s">
-        <v>142</v>
+        <v>198</v>
       </c>
       <c r="J15" t="s">
-        <v>166</v>
+        <v>233</v>
       </c>
       <c r="K15" t="s">
-        <v>167</v>
+        <v>234</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -1980,34 +3170,34 @@
         <v>3</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C16">
         <v>5</v>
       </c>
       <c r="D16" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="E16" t="s">
-        <v>169</v>
+        <v>222</v>
       </c>
       <c r="F16" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="G16" t="s">
-        <v>123</v>
+        <v>186</v>
       </c>
       <c r="H16" t="s">
-        <v>124</v>
+        <v>187</v>
       </c>
       <c r="I16" t="s">
-        <v>94</v>
+        <v>202</v>
       </c>
       <c r="J16" t="s">
-        <v>171</v>
+        <v>235</v>
       </c>
       <c r="K16" t="s">
-        <v>172</v>
+        <v>225</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -2015,34 +3205,34 @@
         <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
       <c r="D17" t="s">
-        <v>89</v>
+        <v>184</v>
       </c>
       <c r="E17" t="s">
-        <v>173</v>
+        <v>236</v>
       </c>
       <c r="F17" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="G17" t="s">
-        <v>92</v>
+        <v>186</v>
       </c>
       <c r="H17" t="s">
-        <v>93</v>
+        <v>187</v>
       </c>
       <c r="I17" t="s">
-        <v>94</v>
+        <v>188</v>
       </c>
       <c r="J17" t="s">
-        <v>175</v>
+        <v>237</v>
       </c>
       <c r="K17" t="s">
-        <v>176</v>
+        <v>238</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -2050,34 +3240,34 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C18">
         <v>2</v>
       </c>
       <c r="D18" t="s">
-        <v>97</v>
+        <v>184</v>
       </c>
       <c r="E18" t="s">
-        <v>177</v>
+        <v>239</v>
       </c>
       <c r="F18" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="G18" t="s">
-        <v>100</v>
+        <v>192</v>
       </c>
       <c r="H18" t="s">
-        <v>101</v>
+        <v>193</v>
       </c>
       <c r="I18" t="s">
-        <v>102</v>
+        <v>212</v>
       </c>
       <c r="J18" t="s">
-        <v>179</v>
+        <v>240</v>
       </c>
       <c r="K18" t="s">
-        <v>180</v>
+        <v>241</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -2085,34 +3275,34 @@
         <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C19">
         <v>3</v>
       </c>
       <c r="D19" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E19" t="s">
-        <v>182</v>
+        <v>242</v>
       </c>
       <c r="F19" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G19" t="s">
-        <v>108</v>
+        <v>186</v>
       </c>
       <c r="H19" t="s">
-        <v>109</v>
+        <v>187</v>
       </c>
       <c r="I19" t="s">
-        <v>110</v>
+        <v>198</v>
       </c>
       <c r="J19" t="s">
-        <v>184</v>
+        <v>243</v>
       </c>
       <c r="K19" t="s">
-        <v>185</v>
+        <v>244</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -2120,34 +3310,34 @@
         <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C20">
         <v>4</v>
       </c>
       <c r="D20" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E20" t="s">
-        <v>187</v>
+        <v>245</v>
       </c>
       <c r="F20" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="G20" t="s">
-        <v>116</v>
+        <v>192</v>
       </c>
       <c r="H20" t="s">
-        <v>117</v>
+        <v>193</v>
       </c>
       <c r="I20" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="J20" t="s">
-        <v>189</v>
+        <v>246</v>
       </c>
       <c r="K20" t="s">
-        <v>190</v>
+        <v>247</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -2155,34 +3345,2834 @@
         <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C21">
         <v>5</v>
       </c>
       <c r="D21" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="E21" t="s">
+        <v>236</v>
+      </c>
+      <c r="F21" t="s">
+        <v>184</v>
+      </c>
+      <c r="G21" t="s">
+        <v>186</v>
+      </c>
+      <c r="H21" t="s">
+        <v>187</v>
+      </c>
+      <c r="I21" t="s">
+        <v>248</v>
+      </c>
+      <c r="J21" t="s">
+        <v>249</v>
+      </c>
+      <c r="K21" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>5</v>
+      </c>
+      <c r="B22" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22" t="s">
+        <v>184</v>
+      </c>
+      <c r="E22" t="s">
+        <v>250</v>
+      </c>
+      <c r="F22" t="s">
+        <v>184</v>
+      </c>
+      <c r="G22" t="s">
+        <v>186</v>
+      </c>
+      <c r="H22" t="s">
+        <v>187</v>
+      </c>
+      <c r="I22" t="s">
+        <v>188</v>
+      </c>
+      <c r="J22" t="s">
+        <v>251</v>
+      </c>
+      <c r="K22" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>5</v>
+      </c>
+      <c r="B23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+      <c r="D23" t="s">
+        <v>184</v>
+      </c>
+      <c r="E23" t="s">
+        <v>253</v>
+      </c>
+      <c r="F23" t="s">
+        <v>184</v>
+      </c>
+      <c r="G23" t="s">
+        <v>205</v>
+      </c>
+      <c r="H23" t="s">
+        <v>206</v>
+      </c>
+      <c r="I23" t="s">
+        <v>202</v>
+      </c>
+      <c r="J23" t="s">
+        <v>254</v>
+      </c>
+      <c r="K23" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>5</v>
+      </c>
+      <c r="B24" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24">
+        <v>3</v>
+      </c>
+      <c r="D24" t="s">
+        <v>184</v>
+      </c>
+      <c r="E24" t="s">
+        <v>256</v>
+      </c>
+      <c r="F24" t="s">
+        <v>184</v>
+      </c>
+      <c r="G24" t="s">
         <v>192</v>
       </c>
-      <c r="F21" t="s">
+      <c r="H24" t="s">
         <v>193</v>
       </c>
-      <c r="G21" t="s">
-        <v>123</v>
-      </c>
-      <c r="H21" t="s">
-        <v>124</v>
-      </c>
-      <c r="I21" t="s">
-        <v>94</v>
-      </c>
-      <c r="J21" t="s">
+      <c r="I24" t="s">
+        <v>223</v>
+      </c>
+      <c r="J24" t="s">
+        <v>257</v>
+      </c>
+      <c r="K24" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>5</v>
+      </c>
+      <c r="B25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25">
+        <v>4</v>
+      </c>
+      <c r="D25" t="s">
+        <v>184</v>
+      </c>
+      <c r="E25" t="s">
+        <v>259</v>
+      </c>
+      <c r="F25" t="s">
+        <v>184</v>
+      </c>
+      <c r="G25" t="s">
+        <v>186</v>
+      </c>
+      <c r="H25" t="s">
+        <v>187</v>
+      </c>
+      <c r="I25" t="s">
+        <v>260</v>
+      </c>
+      <c r="J25" t="s">
+        <v>261</v>
+      </c>
+      <c r="K25" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>5</v>
+      </c>
+      <c r="B26" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26">
+        <v>5</v>
+      </c>
+      <c r="D26" t="s">
+        <v>184</v>
+      </c>
+      <c r="E26" t="s">
+        <v>250</v>
+      </c>
+      <c r="F26" t="s">
+        <v>184</v>
+      </c>
+      <c r="G26" t="s">
+        <v>186</v>
+      </c>
+      <c r="H26" t="s">
+        <v>187</v>
+      </c>
+      <c r="I26" t="s">
+        <v>188</v>
+      </c>
+      <c r="J26" t="s">
+        <v>263</v>
+      </c>
+      <c r="K26" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>6</v>
+      </c>
+      <c r="B27" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27" t="s">
+        <v>184</v>
+      </c>
+      <c r="E27" t="s">
+        <v>264</v>
+      </c>
+      <c r="F27" t="s">
+        <v>184</v>
+      </c>
+      <c r="G27" t="s">
+        <v>192</v>
+      </c>
+      <c r="H27" t="s">
+        <v>193</v>
+      </c>
+      <c r="I27" t="s">
+        <v>260</v>
+      </c>
+      <c r="J27" t="s">
+        <v>265</v>
+      </c>
+      <c r="K27" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>6</v>
+      </c>
+      <c r="B28" t="s">
+        <v>40</v>
+      </c>
+      <c r="C28">
+        <v>2</v>
+      </c>
+      <c r="D28" t="s">
+        <v>184</v>
+      </c>
+      <c r="E28" t="s">
+        <v>267</v>
+      </c>
+      <c r="F28" t="s">
+        <v>184</v>
+      </c>
+      <c r="G28" t="s">
+        <v>192</v>
+      </c>
+      <c r="H28" t="s">
+        <v>193</v>
+      </c>
+      <c r="I28" t="s">
+        <v>212</v>
+      </c>
+      <c r="J28" t="s">
+        <v>268</v>
+      </c>
+      <c r="K28" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>6</v>
+      </c>
+      <c r="B29" t="s">
+        <v>40</v>
+      </c>
+      <c r="C29">
+        <v>3</v>
+      </c>
+      <c r="D29" t="s">
+        <v>184</v>
+      </c>
+      <c r="E29" t="s">
+        <v>270</v>
+      </c>
+      <c r="F29" t="s">
+        <v>184</v>
+      </c>
+      <c r="G29" t="s">
+        <v>186</v>
+      </c>
+      <c r="H29" t="s">
+        <v>187</v>
+      </c>
+      <c r="I29" t="s">
+        <v>198</v>
+      </c>
+      <c r="J29" t="s">
+        <v>271</v>
+      </c>
+      <c r="K29" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>6</v>
+      </c>
+      <c r="B30" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30">
+        <v>4</v>
+      </c>
+      <c r="D30" t="s">
+        <v>184</v>
+      </c>
+      <c r="E30" t="s">
+        <v>273</v>
+      </c>
+      <c r="F30" t="s">
+        <v>184</v>
+      </c>
+      <c r="G30" t="s">
+        <v>186</v>
+      </c>
+      <c r="H30" t="s">
+        <v>187</v>
+      </c>
+      <c r="I30" t="s">
         <v>194</v>
       </c>
-      <c r="K21" t="s">
-        <v>195</v>
+      <c r="J30" t="s">
+        <v>274</v>
+      </c>
+      <c r="K30" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>6</v>
+      </c>
+      <c r="B31" t="s">
+        <v>40</v>
+      </c>
+      <c r="C31">
+        <v>5</v>
+      </c>
+      <c r="D31" t="s">
+        <v>184</v>
+      </c>
+      <c r="E31" t="s">
+        <v>264</v>
+      </c>
+      <c r="F31" t="s">
+        <v>184</v>
+      </c>
+      <c r="G31" t="s">
+        <v>186</v>
+      </c>
+      <c r="H31" t="s">
+        <v>187</v>
+      </c>
+      <c r="I31" t="s">
+        <v>202</v>
+      </c>
+      <c r="J31" t="s">
+        <v>276</v>
+      </c>
+      <c r="K31" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>7</v>
+      </c>
+      <c r="B32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32" t="s">
+        <v>184</v>
+      </c>
+      <c r="E32" t="s">
+        <v>277</v>
+      </c>
+      <c r="F32" t="s">
+        <v>184</v>
+      </c>
+      <c r="G32" t="s">
+        <v>186</v>
+      </c>
+      <c r="H32" t="s">
+        <v>187</v>
+      </c>
+      <c r="I32" t="s">
+        <v>223</v>
+      </c>
+      <c r="J32" t="s">
+        <v>278</v>
+      </c>
+      <c r="K32" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>7</v>
+      </c>
+      <c r="B33" t="s">
+        <v>45</v>
+      </c>
+      <c r="C33">
+        <v>2</v>
+      </c>
+      <c r="D33" t="s">
+        <v>184</v>
+      </c>
+      <c r="E33" t="s">
+        <v>280</v>
+      </c>
+      <c r="F33" t="s">
+        <v>184</v>
+      </c>
+      <c r="G33" t="s">
+        <v>192</v>
+      </c>
+      <c r="H33" t="s">
+        <v>193</v>
+      </c>
+      <c r="I33" t="s">
+        <v>223</v>
+      </c>
+      <c r="J33" t="s">
+        <v>281</v>
+      </c>
+      <c r="K33" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>7</v>
+      </c>
+      <c r="B34" t="s">
+        <v>45</v>
+      </c>
+      <c r="C34">
+        <v>3</v>
+      </c>
+      <c r="D34" t="s">
+        <v>184</v>
+      </c>
+      <c r="E34" t="s">
+        <v>283</v>
+      </c>
+      <c r="F34" t="s">
+        <v>184</v>
+      </c>
+      <c r="G34" t="s">
+        <v>186</v>
+      </c>
+      <c r="H34" t="s">
+        <v>187</v>
+      </c>
+      <c r="I34" t="s">
+        <v>194</v>
+      </c>
+      <c r="J34" t="s">
+        <v>284</v>
+      </c>
+      <c r="K34" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>7</v>
+      </c>
+      <c r="B35" t="s">
+        <v>45</v>
+      </c>
+      <c r="C35">
+        <v>4</v>
+      </c>
+      <c r="D35" t="s">
+        <v>184</v>
+      </c>
+      <c r="E35" t="s">
+        <v>286</v>
+      </c>
+      <c r="F35" t="s">
+        <v>184</v>
+      </c>
+      <c r="G35" t="s">
+        <v>186</v>
+      </c>
+      <c r="H35" t="s">
+        <v>187</v>
+      </c>
+      <c r="I35" t="s">
+        <v>198</v>
+      </c>
+      <c r="J35" t="s">
+        <v>287</v>
+      </c>
+      <c r="K35" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>7</v>
+      </c>
+      <c r="B36" t="s">
+        <v>45</v>
+      </c>
+      <c r="C36">
+        <v>5</v>
+      </c>
+      <c r="D36" t="s">
+        <v>184</v>
+      </c>
+      <c r="E36" t="s">
+        <v>277</v>
+      </c>
+      <c r="F36" t="s">
+        <v>184</v>
+      </c>
+      <c r="G36" t="s">
+        <v>192</v>
+      </c>
+      <c r="H36" t="s">
+        <v>193</v>
+      </c>
+      <c r="I36" t="s">
+        <v>202</v>
+      </c>
+      <c r="J36" t="s">
+        <v>289</v>
+      </c>
+      <c r="K36" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>8</v>
+      </c>
+      <c r="B37" t="s">
+        <v>50</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37" t="s">
+        <v>184</v>
+      </c>
+      <c r="E37" t="s">
+        <v>290</v>
+      </c>
+      <c r="F37" t="s">
+        <v>184</v>
+      </c>
+      <c r="G37" t="s">
+        <v>186</v>
+      </c>
+      <c r="H37" t="s">
+        <v>187</v>
+      </c>
+      <c r="I37" t="s">
+        <v>212</v>
+      </c>
+      <c r="J37" t="s">
+        <v>291</v>
+      </c>
+      <c r="K37" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>8</v>
+      </c>
+      <c r="B38" t="s">
+        <v>50</v>
+      </c>
+      <c r="C38">
+        <v>2</v>
+      </c>
+      <c r="D38" t="s">
+        <v>184</v>
+      </c>
+      <c r="E38" t="s">
+        <v>293</v>
+      </c>
+      <c r="F38" t="s">
+        <v>184</v>
+      </c>
+      <c r="G38" t="s">
+        <v>186</v>
+      </c>
+      <c r="H38" t="s">
+        <v>187</v>
+      </c>
+      <c r="I38" t="s">
+        <v>248</v>
+      </c>
+      <c r="J38" t="s">
+        <v>294</v>
+      </c>
+      <c r="K38" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>8</v>
+      </c>
+      <c r="B39" t="s">
+        <v>50</v>
+      </c>
+      <c r="C39">
+        <v>3</v>
+      </c>
+      <c r="D39" t="s">
+        <v>184</v>
+      </c>
+      <c r="E39" t="s">
+        <v>296</v>
+      </c>
+      <c r="F39" t="s">
+        <v>184</v>
+      </c>
+      <c r="G39" t="s">
+        <v>186</v>
+      </c>
+      <c r="H39" t="s">
+        <v>187</v>
+      </c>
+      <c r="I39" t="s">
+        <v>194</v>
+      </c>
+      <c r="J39" t="s">
+        <v>297</v>
+      </c>
+      <c r="K39" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>8</v>
+      </c>
+      <c r="B40" t="s">
+        <v>50</v>
+      </c>
+      <c r="C40">
+        <v>4</v>
+      </c>
+      <c r="D40" t="s">
+        <v>184</v>
+      </c>
+      <c r="E40" t="s">
+        <v>299</v>
+      </c>
+      <c r="F40" t="s">
+        <v>184</v>
+      </c>
+      <c r="G40" t="s">
+        <v>192</v>
+      </c>
+      <c r="H40" t="s">
+        <v>193</v>
+      </c>
+      <c r="I40" t="s">
+        <v>198</v>
+      </c>
+      <c r="J40" t="s">
+        <v>300</v>
+      </c>
+      <c r="K40" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>8</v>
+      </c>
+      <c r="B41" t="s">
+        <v>50</v>
+      </c>
+      <c r="C41">
+        <v>5</v>
+      </c>
+      <c r="D41" t="s">
+        <v>184</v>
+      </c>
+      <c r="E41" t="s">
+        <v>290</v>
+      </c>
+      <c r="F41" t="s">
+        <v>184</v>
+      </c>
+      <c r="G41" t="s">
+        <v>192</v>
+      </c>
+      <c r="H41" t="s">
+        <v>193</v>
+      </c>
+      <c r="I41" t="s">
+        <v>202</v>
+      </c>
+      <c r="J41" t="s">
+        <v>302</v>
+      </c>
+      <c r="K41" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>9</v>
+      </c>
+      <c r="B42" t="s">
+        <v>56</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+      <c r="D42" t="s">
+        <v>184</v>
+      </c>
+      <c r="E42" t="s">
+        <v>303</v>
+      </c>
+      <c r="F42" t="s">
+        <v>184</v>
+      </c>
+      <c r="G42" t="s">
+        <v>192</v>
+      </c>
+      <c r="H42" t="s">
+        <v>193</v>
+      </c>
+      <c r="I42" t="s">
+        <v>248</v>
+      </c>
+      <c r="J42" t="s">
+        <v>304</v>
+      </c>
+      <c r="K42" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>9</v>
+      </c>
+      <c r="B43" t="s">
+        <v>56</v>
+      </c>
+      <c r="C43">
+        <v>2</v>
+      </c>
+      <c r="D43" t="s">
+        <v>184</v>
+      </c>
+      <c r="E43" t="s">
+        <v>306</v>
+      </c>
+      <c r="F43" t="s">
+        <v>184</v>
+      </c>
+      <c r="G43" t="s">
+        <v>186</v>
+      </c>
+      <c r="H43" t="s">
+        <v>187</v>
+      </c>
+      <c r="I43" t="s">
+        <v>223</v>
+      </c>
+      <c r="J43" t="s">
+        <v>307</v>
+      </c>
+      <c r="K43" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>9</v>
+      </c>
+      <c r="B44" t="s">
+        <v>56</v>
+      </c>
+      <c r="C44">
+        <v>3</v>
+      </c>
+      <c r="D44" t="s">
+        <v>184</v>
+      </c>
+      <c r="E44" t="s">
+        <v>309</v>
+      </c>
+      <c r="F44" t="s">
+        <v>184</v>
+      </c>
+      <c r="G44" t="s">
+        <v>186</v>
+      </c>
+      <c r="H44" t="s">
+        <v>187</v>
+      </c>
+      <c r="I44" t="s">
+        <v>248</v>
+      </c>
+      <c r="J44" t="s">
+        <v>310</v>
+      </c>
+      <c r="K44" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>9</v>
+      </c>
+      <c r="B45" t="s">
+        <v>56</v>
+      </c>
+      <c r="C45">
+        <v>4</v>
+      </c>
+      <c r="D45" t="s">
+        <v>184</v>
+      </c>
+      <c r="E45" t="s">
+        <v>312</v>
+      </c>
+      <c r="F45" t="s">
+        <v>184</v>
+      </c>
+      <c r="G45" t="s">
+        <v>205</v>
+      </c>
+      <c r="H45" t="s">
+        <v>206</v>
+      </c>
+      <c r="I45" t="s">
+        <v>248</v>
+      </c>
+      <c r="J45" t="s">
+        <v>313</v>
+      </c>
+      <c r="K45" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>9</v>
+      </c>
+      <c r="B46" t="s">
+        <v>56</v>
+      </c>
+      <c r="C46">
+        <v>5</v>
+      </c>
+      <c r="D46" t="s">
+        <v>184</v>
+      </c>
+      <c r="E46" t="s">
+        <v>303</v>
+      </c>
+      <c r="F46" t="s">
+        <v>184</v>
+      </c>
+      <c r="G46" t="s">
+        <v>192</v>
+      </c>
+      <c r="H46" t="s">
+        <v>193</v>
+      </c>
+      <c r="I46" t="s">
+        <v>223</v>
+      </c>
+      <c r="J46" t="s">
+        <v>315</v>
+      </c>
+      <c r="K46" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>10</v>
+      </c>
+      <c r="B47" t="s">
+        <v>63</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+      <c r="D47" t="s">
+        <v>184</v>
+      </c>
+      <c r="E47" t="s">
+        <v>316</v>
+      </c>
+      <c r="F47" t="s">
+        <v>184</v>
+      </c>
+      <c r="G47" t="s">
+        <v>192</v>
+      </c>
+      <c r="H47" t="s">
+        <v>193</v>
+      </c>
+      <c r="I47" t="s">
+        <v>212</v>
+      </c>
+      <c r="J47" t="s">
+        <v>317</v>
+      </c>
+      <c r="K47" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>10</v>
+      </c>
+      <c r="B48" t="s">
+        <v>63</v>
+      </c>
+      <c r="C48">
+        <v>2</v>
+      </c>
+      <c r="D48" t="s">
+        <v>184</v>
+      </c>
+      <c r="E48" t="s">
+        <v>319</v>
+      </c>
+      <c r="F48" t="s">
+        <v>184</v>
+      </c>
+      <c r="G48" t="s">
+        <v>186</v>
+      </c>
+      <c r="H48" t="s">
+        <v>187</v>
+      </c>
+      <c r="I48" t="s">
+        <v>188</v>
+      </c>
+      <c r="J48" t="s">
+        <v>320</v>
+      </c>
+      <c r="K48" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>10</v>
+      </c>
+      <c r="B49" t="s">
+        <v>63</v>
+      </c>
+      <c r="C49">
+        <v>3</v>
+      </c>
+      <c r="D49" t="s">
+        <v>184</v>
+      </c>
+      <c r="E49" t="s">
+        <v>322</v>
+      </c>
+      <c r="F49" t="s">
+        <v>184</v>
+      </c>
+      <c r="G49" t="s">
+        <v>186</v>
+      </c>
+      <c r="H49" t="s">
+        <v>187</v>
+      </c>
+      <c r="I49" t="s">
+        <v>198</v>
+      </c>
+      <c r="J49" t="s">
+        <v>323</v>
+      </c>
+      <c r="K49" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>10</v>
+      </c>
+      <c r="B50" t="s">
+        <v>63</v>
+      </c>
+      <c r="C50">
+        <v>4</v>
+      </c>
+      <c r="D50" t="s">
+        <v>184</v>
+      </c>
+      <c r="E50" t="s">
+        <v>325</v>
+      </c>
+      <c r="F50" t="s">
+        <v>184</v>
+      </c>
+      <c r="G50" t="s">
+        <v>192</v>
+      </c>
+      <c r="H50" t="s">
+        <v>193</v>
+      </c>
+      <c r="I50" t="s">
+        <v>194</v>
+      </c>
+      <c r="J50" t="s">
+        <v>326</v>
+      </c>
+      <c r="K50" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>10</v>
+      </c>
+      <c r="B51" t="s">
+        <v>63</v>
+      </c>
+      <c r="C51">
+        <v>5</v>
+      </c>
+      <c r="D51" t="s">
+        <v>184</v>
+      </c>
+      <c r="E51" t="s">
+        <v>316</v>
+      </c>
+      <c r="F51" t="s">
+        <v>184</v>
+      </c>
+      <c r="G51" t="s">
+        <v>186</v>
+      </c>
+      <c r="H51" t="s">
+        <v>187</v>
+      </c>
+      <c r="I51" t="s">
+        <v>202</v>
+      </c>
+      <c r="J51" t="s">
+        <v>328</v>
+      </c>
+      <c r="K51" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>11</v>
+      </c>
+      <c r="B52" t="s">
+        <v>68</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+      <c r="D52" t="s">
+        <v>184</v>
+      </c>
+      <c r="E52" t="s">
+        <v>329</v>
+      </c>
+      <c r="F52" t="s">
+        <v>184</v>
+      </c>
+      <c r="G52" t="s">
+        <v>192</v>
+      </c>
+      <c r="H52" t="s">
+        <v>193</v>
+      </c>
+      <c r="I52" t="s">
+        <v>212</v>
+      </c>
+      <c r="J52" t="s">
+        <v>330</v>
+      </c>
+      <c r="K52" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>11</v>
+      </c>
+      <c r="B53" t="s">
+        <v>68</v>
+      </c>
+      <c r="C53">
+        <v>2</v>
+      </c>
+      <c r="D53" t="s">
+        <v>184</v>
+      </c>
+      <c r="E53" t="s">
+        <v>332</v>
+      </c>
+      <c r="F53" t="s">
+        <v>184</v>
+      </c>
+      <c r="G53" t="s">
+        <v>186</v>
+      </c>
+      <c r="H53" t="s">
+        <v>187</v>
+      </c>
+      <c r="I53" t="s">
+        <v>194</v>
+      </c>
+      <c r="J53" t="s">
+        <v>333</v>
+      </c>
+      <c r="K53" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>11</v>
+      </c>
+      <c r="B54" t="s">
+        <v>68</v>
+      </c>
+      <c r="C54">
+        <v>3</v>
+      </c>
+      <c r="D54" t="s">
+        <v>184</v>
+      </c>
+      <c r="E54" t="s">
+        <v>335</v>
+      </c>
+      <c r="F54" t="s">
+        <v>184</v>
+      </c>
+      <c r="G54" t="s">
+        <v>186</v>
+      </c>
+      <c r="H54" t="s">
+        <v>187</v>
+      </c>
+      <c r="I54" t="s">
+        <v>202</v>
+      </c>
+      <c r="J54" t="s">
+        <v>336</v>
+      </c>
+      <c r="K54" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>11</v>
+      </c>
+      <c r="B55" t="s">
+        <v>68</v>
+      </c>
+      <c r="C55">
+        <v>4</v>
+      </c>
+      <c r="D55" t="s">
+        <v>184</v>
+      </c>
+      <c r="E55" t="s">
+        <v>338</v>
+      </c>
+      <c r="F55" t="s">
+        <v>184</v>
+      </c>
+      <c r="G55" t="s">
+        <v>186</v>
+      </c>
+      <c r="H55" t="s">
+        <v>187</v>
+      </c>
+      <c r="I55" t="s">
+        <v>212</v>
+      </c>
+      <c r="J55" t="s">
+        <v>339</v>
+      </c>
+      <c r="K55" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>11</v>
+      </c>
+      <c r="B56" t="s">
+        <v>68</v>
+      </c>
+      <c r="C56">
+        <v>5</v>
+      </c>
+      <c r="D56" t="s">
+        <v>184</v>
+      </c>
+      <c r="E56" t="s">
+        <v>329</v>
+      </c>
+      <c r="F56" t="s">
+        <v>184</v>
+      </c>
+      <c r="G56" t="s">
+        <v>205</v>
+      </c>
+      <c r="H56" t="s">
+        <v>206</v>
+      </c>
+      <c r="I56" t="s">
+        <v>248</v>
+      </c>
+      <c r="J56" t="s">
+        <v>341</v>
+      </c>
+      <c r="K56" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>12</v>
+      </c>
+      <c r="B57" t="s">
+        <v>74</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
+      <c r="D57" t="s">
+        <v>184</v>
+      </c>
+      <c r="E57" t="s">
+        <v>342</v>
+      </c>
+      <c r="F57" t="s">
+        <v>184</v>
+      </c>
+      <c r="G57" t="s">
+        <v>186</v>
+      </c>
+      <c r="H57" t="s">
+        <v>187</v>
+      </c>
+      <c r="I57" t="s">
+        <v>188</v>
+      </c>
+      <c r="J57" t="s">
+        <v>343</v>
+      </c>
+      <c r="K57" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>12</v>
+      </c>
+      <c r="B58" t="s">
+        <v>74</v>
+      </c>
+      <c r="C58">
+        <v>2</v>
+      </c>
+      <c r="D58" t="s">
+        <v>184</v>
+      </c>
+      <c r="E58" t="s">
+        <v>345</v>
+      </c>
+      <c r="F58" t="s">
+        <v>184</v>
+      </c>
+      <c r="G58" t="s">
+        <v>192</v>
+      </c>
+      <c r="H58" t="s">
+        <v>193</v>
+      </c>
+      <c r="I58" t="s">
+        <v>248</v>
+      </c>
+      <c r="J58" t="s">
+        <v>346</v>
+      </c>
+      <c r="K58" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>12</v>
+      </c>
+      <c r="B59" t="s">
+        <v>74</v>
+      </c>
+      <c r="C59">
+        <v>3</v>
+      </c>
+      <c r="D59" t="s">
+        <v>184</v>
+      </c>
+      <c r="E59" t="s">
+        <v>348</v>
+      </c>
+      <c r="F59" t="s">
+        <v>184</v>
+      </c>
+      <c r="G59" t="s">
+        <v>186</v>
+      </c>
+      <c r="H59" t="s">
+        <v>187</v>
+      </c>
+      <c r="I59" t="s">
+        <v>223</v>
+      </c>
+      <c r="J59" t="s">
+        <v>349</v>
+      </c>
+      <c r="K59" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>12</v>
+      </c>
+      <c r="B60" t="s">
+        <v>74</v>
+      </c>
+      <c r="C60">
+        <v>4</v>
+      </c>
+      <c r="D60" t="s">
+        <v>184</v>
+      </c>
+      <c r="E60" t="s">
+        <v>351</v>
+      </c>
+      <c r="F60" t="s">
+        <v>184</v>
+      </c>
+      <c r="G60" t="s">
+        <v>186</v>
+      </c>
+      <c r="H60" t="s">
+        <v>187</v>
+      </c>
+      <c r="I60" t="s">
+        <v>212</v>
+      </c>
+      <c r="J60" t="s">
+        <v>352</v>
+      </c>
+      <c r="K60" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>12</v>
+      </c>
+      <c r="B61" t="s">
+        <v>74</v>
+      </c>
+      <c r="C61">
+        <v>5</v>
+      </c>
+      <c r="D61" t="s">
+        <v>184</v>
+      </c>
+      <c r="E61" t="s">
+        <v>342</v>
+      </c>
+      <c r="F61" t="s">
+        <v>184</v>
+      </c>
+      <c r="G61" t="s">
+        <v>192</v>
+      </c>
+      <c r="H61" t="s">
+        <v>193</v>
+      </c>
+      <c r="I61" t="s">
+        <v>202</v>
+      </c>
+      <c r="J61" t="s">
+        <v>354</v>
+      </c>
+      <c r="K61" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>13</v>
+      </c>
+      <c r="B62" t="s">
+        <v>81</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
+      <c r="D62" t="s">
+        <v>184</v>
+      </c>
+      <c r="E62" t="s">
+        <v>355</v>
+      </c>
+      <c r="F62" t="s">
+        <v>184</v>
+      </c>
+      <c r="G62" t="s">
+        <v>186</v>
+      </c>
+      <c r="H62" t="s">
+        <v>187</v>
+      </c>
+      <c r="I62" t="s">
+        <v>188</v>
+      </c>
+      <c r="J62" t="s">
+        <v>356</v>
+      </c>
+      <c r="K62" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>13</v>
+      </c>
+      <c r="B63" t="s">
+        <v>81</v>
+      </c>
+      <c r="C63">
+        <v>2</v>
+      </c>
+      <c r="D63" t="s">
+        <v>184</v>
+      </c>
+      <c r="E63" t="s">
+        <v>358</v>
+      </c>
+      <c r="F63" t="s">
+        <v>184</v>
+      </c>
+      <c r="G63" t="s">
+        <v>186</v>
+      </c>
+      <c r="H63" t="s">
+        <v>187</v>
+      </c>
+      <c r="I63" t="s">
+        <v>194</v>
+      </c>
+      <c r="J63" t="s">
+        <v>297</v>
+      </c>
+      <c r="K63" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>13</v>
+      </c>
+      <c r="B64" t="s">
+        <v>81</v>
+      </c>
+      <c r="C64">
+        <v>3</v>
+      </c>
+      <c r="D64" t="s">
+        <v>184</v>
+      </c>
+      <c r="E64" t="s">
+        <v>360</v>
+      </c>
+      <c r="F64" t="s">
+        <v>184</v>
+      </c>
+      <c r="G64" t="s">
+        <v>186</v>
+      </c>
+      <c r="H64" t="s">
+        <v>187</v>
+      </c>
+      <c r="I64" t="s">
+        <v>198</v>
+      </c>
+      <c r="J64" t="s">
+        <v>361</v>
+      </c>
+      <c r="K64" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>13</v>
+      </c>
+      <c r="B65" t="s">
+        <v>81</v>
+      </c>
+      <c r="C65">
+        <v>4</v>
+      </c>
+      <c r="D65" t="s">
+        <v>184</v>
+      </c>
+      <c r="E65" t="s">
+        <v>363</v>
+      </c>
+      <c r="F65" t="s">
+        <v>184</v>
+      </c>
+      <c r="G65" t="s">
+        <v>192</v>
+      </c>
+      <c r="H65" t="s">
+        <v>193</v>
+      </c>
+      <c r="I65" t="s">
+        <v>198</v>
+      </c>
+      <c r="J65" t="s">
+        <v>364</v>
+      </c>
+      <c r="K65" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>13</v>
+      </c>
+      <c r="B66" t="s">
+        <v>81</v>
+      </c>
+      <c r="C66">
+        <v>5</v>
+      </c>
+      <c r="D66" t="s">
+        <v>184</v>
+      </c>
+      <c r="E66" t="s">
+        <v>355</v>
+      </c>
+      <c r="F66" t="s">
+        <v>184</v>
+      </c>
+      <c r="G66" t="s">
+        <v>186</v>
+      </c>
+      <c r="H66" t="s">
+        <v>187</v>
+      </c>
+      <c r="I66" t="s">
+        <v>202</v>
+      </c>
+      <c r="J66" t="s">
+        <v>366</v>
+      </c>
+      <c r="K66" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>14</v>
+      </c>
+      <c r="B67" t="s">
+        <v>88</v>
+      </c>
+      <c r="C67">
+        <v>1</v>
+      </c>
+      <c r="D67" t="s">
+        <v>184</v>
+      </c>
+      <c r="E67" t="s">
+        <v>367</v>
+      </c>
+      <c r="F67" t="s">
+        <v>184</v>
+      </c>
+      <c r="G67" t="s">
+        <v>186</v>
+      </c>
+      <c r="H67" t="s">
+        <v>187</v>
+      </c>
+      <c r="I67" t="s">
+        <v>188</v>
+      </c>
+      <c r="J67" t="s">
+        <v>368</v>
+      </c>
+      <c r="K67" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>14</v>
+      </c>
+      <c r="B68" t="s">
+        <v>88</v>
+      </c>
+      <c r="C68">
+        <v>2</v>
+      </c>
+      <c r="D68" t="s">
+        <v>184</v>
+      </c>
+      <c r="E68" t="s">
+        <v>370</v>
+      </c>
+      <c r="F68" t="s">
+        <v>184</v>
+      </c>
+      <c r="G68" t="s">
+        <v>186</v>
+      </c>
+      <c r="H68" t="s">
+        <v>187</v>
+      </c>
+      <c r="I68" t="s">
+        <v>223</v>
+      </c>
+      <c r="J68" t="s">
+        <v>371</v>
+      </c>
+      <c r="K68" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>14</v>
+      </c>
+      <c r="B69" t="s">
+        <v>88</v>
+      </c>
+      <c r="C69">
+        <v>3</v>
+      </c>
+      <c r="D69" t="s">
+        <v>184</v>
+      </c>
+      <c r="E69" t="s">
+        <v>373</v>
+      </c>
+      <c r="F69" t="s">
+        <v>184</v>
+      </c>
+      <c r="G69" t="s">
+        <v>192</v>
+      </c>
+      <c r="H69" t="s">
+        <v>193</v>
+      </c>
+      <c r="I69" t="s">
+        <v>198</v>
+      </c>
+      <c r="J69" t="s">
+        <v>374</v>
+      </c>
+      <c r="K69" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>14</v>
+      </c>
+      <c r="B70" t="s">
+        <v>88</v>
+      </c>
+      <c r="C70">
+        <v>4</v>
+      </c>
+      <c r="D70" t="s">
+        <v>184</v>
+      </c>
+      <c r="E70" t="s">
+        <v>376</v>
+      </c>
+      <c r="F70" t="s">
+        <v>184</v>
+      </c>
+      <c r="G70" t="s">
+        <v>205</v>
+      </c>
+      <c r="H70" t="s">
+        <v>206</v>
+      </c>
+      <c r="I70" t="s">
+        <v>248</v>
+      </c>
+      <c r="J70" t="s">
+        <v>377</v>
+      </c>
+      <c r="K70" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>14</v>
+      </c>
+      <c r="B71" t="s">
+        <v>88</v>
+      </c>
+      <c r="C71">
+        <v>5</v>
+      </c>
+      <c r="D71" t="s">
+        <v>184</v>
+      </c>
+      <c r="E71" t="s">
+        <v>367</v>
+      </c>
+      <c r="F71" t="s">
+        <v>184</v>
+      </c>
+      <c r="G71" t="s">
+        <v>186</v>
+      </c>
+      <c r="H71" t="s">
+        <v>187</v>
+      </c>
+      <c r="I71" t="s">
+        <v>202</v>
+      </c>
+      <c r="J71" t="s">
+        <v>379</v>
+      </c>
+      <c r="K71" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>15</v>
+      </c>
+      <c r="B72" t="s">
+        <v>93</v>
+      </c>
+      <c r="C72">
+        <v>1</v>
+      </c>
+      <c r="D72" t="s">
+        <v>184</v>
+      </c>
+      <c r="E72" t="s">
+        <v>380</v>
+      </c>
+      <c r="F72" t="s">
+        <v>184</v>
+      </c>
+      <c r="G72" t="s">
+        <v>186</v>
+      </c>
+      <c r="H72" t="s">
+        <v>187</v>
+      </c>
+      <c r="I72" t="s">
+        <v>212</v>
+      </c>
+      <c r="J72" t="s">
+        <v>381</v>
+      </c>
+      <c r="K72" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>15</v>
+      </c>
+      <c r="B73" t="s">
+        <v>93</v>
+      </c>
+      <c r="C73">
+        <v>2</v>
+      </c>
+      <c r="D73" t="s">
+        <v>184</v>
+      </c>
+      <c r="E73" t="s">
+        <v>383</v>
+      </c>
+      <c r="F73" t="s">
+        <v>184</v>
+      </c>
+      <c r="G73" t="s">
+        <v>192</v>
+      </c>
+      <c r="H73" t="s">
+        <v>193</v>
+      </c>
+      <c r="I73" t="s">
+        <v>248</v>
+      </c>
+      <c r="J73" t="s">
+        <v>384</v>
+      </c>
+      <c r="K73" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>15</v>
+      </c>
+      <c r="B74" t="s">
+        <v>93</v>
+      </c>
+      <c r="C74">
+        <v>3</v>
+      </c>
+      <c r="D74" t="s">
+        <v>184</v>
+      </c>
+      <c r="E74" t="s">
+        <v>386</v>
+      </c>
+      <c r="F74" t="s">
+        <v>184</v>
+      </c>
+      <c r="G74" t="s">
+        <v>186</v>
+      </c>
+      <c r="H74" t="s">
+        <v>187</v>
+      </c>
+      <c r="I74" t="s">
+        <v>248</v>
+      </c>
+      <c r="J74" t="s">
+        <v>387</v>
+      </c>
+      <c r="K74" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>15</v>
+      </c>
+      <c r="B75" t="s">
+        <v>93</v>
+      </c>
+      <c r="C75">
+        <v>4</v>
+      </c>
+      <c r="D75" t="s">
+        <v>184</v>
+      </c>
+      <c r="E75" t="s">
+        <v>389</v>
+      </c>
+      <c r="F75" t="s">
+        <v>184</v>
+      </c>
+      <c r="G75" t="s">
+        <v>186</v>
+      </c>
+      <c r="H75" t="s">
+        <v>187</v>
+      </c>
+      <c r="I75" t="s">
+        <v>188</v>
+      </c>
+      <c r="J75" t="s">
+        <v>390</v>
+      </c>
+      <c r="K75" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>15</v>
+      </c>
+      <c r="B76" t="s">
+        <v>93</v>
+      </c>
+      <c r="C76">
+        <v>5</v>
+      </c>
+      <c r="D76" t="s">
+        <v>184</v>
+      </c>
+      <c r="E76" t="s">
+        <v>380</v>
+      </c>
+      <c r="F76" t="s">
+        <v>184</v>
+      </c>
+      <c r="G76" t="s">
+        <v>186</v>
+      </c>
+      <c r="H76" t="s">
+        <v>187</v>
+      </c>
+      <c r="I76" t="s">
+        <v>212</v>
+      </c>
+      <c r="J76" t="s">
+        <v>392</v>
+      </c>
+      <c r="K76" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>16</v>
+      </c>
+      <c r="B77" t="s">
+        <v>99</v>
+      </c>
+      <c r="C77">
+        <v>1</v>
+      </c>
+      <c r="D77" t="s">
+        <v>184</v>
+      </c>
+      <c r="E77" t="s">
+        <v>393</v>
+      </c>
+      <c r="F77" t="s">
+        <v>184</v>
+      </c>
+      <c r="G77" t="s">
+        <v>186</v>
+      </c>
+      <c r="H77" t="s">
+        <v>187</v>
+      </c>
+      <c r="I77" t="s">
+        <v>212</v>
+      </c>
+      <c r="J77" t="s">
+        <v>394</v>
+      </c>
+      <c r="K77" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>16</v>
+      </c>
+      <c r="B78" t="s">
+        <v>99</v>
+      </c>
+      <c r="C78">
+        <v>2</v>
+      </c>
+      <c r="D78" t="s">
+        <v>184</v>
+      </c>
+      <c r="E78" t="s">
+        <v>396</v>
+      </c>
+      <c r="F78" t="s">
+        <v>184</v>
+      </c>
+      <c r="G78" t="s">
+        <v>192</v>
+      </c>
+      <c r="H78" t="s">
+        <v>193</v>
+      </c>
+      <c r="I78" t="s">
+        <v>248</v>
+      </c>
+      <c r="J78" t="s">
+        <v>397</v>
+      </c>
+      <c r="K78" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>16</v>
+      </c>
+      <c r="B79" t="s">
+        <v>99</v>
+      </c>
+      <c r="C79">
+        <v>3</v>
+      </c>
+      <c r="D79" t="s">
+        <v>184</v>
+      </c>
+      <c r="E79" t="s">
+        <v>399</v>
+      </c>
+      <c r="F79" t="s">
+        <v>184</v>
+      </c>
+      <c r="G79" t="s">
+        <v>186</v>
+      </c>
+      <c r="H79" t="s">
+        <v>187</v>
+      </c>
+      <c r="I79" t="s">
+        <v>188</v>
+      </c>
+      <c r="J79" t="s">
+        <v>400</v>
+      </c>
+      <c r="K79" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>16</v>
+      </c>
+      <c r="B80" t="s">
+        <v>99</v>
+      </c>
+      <c r="C80">
+        <v>4</v>
+      </c>
+      <c r="D80" t="s">
+        <v>184</v>
+      </c>
+      <c r="E80" t="s">
+        <v>402</v>
+      </c>
+      <c r="F80" t="s">
+        <v>184</v>
+      </c>
+      <c r="G80" t="s">
+        <v>403</v>
+      </c>
+      <c r="H80" t="s">
+        <v>404</v>
+      </c>
+      <c r="I80" t="s">
+        <v>202</v>
+      </c>
+      <c r="J80" t="s">
+        <v>405</v>
+      </c>
+      <c r="K80" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>16</v>
+      </c>
+      <c r="B81" t="s">
+        <v>99</v>
+      </c>
+      <c r="C81">
+        <v>5</v>
+      </c>
+      <c r="D81" t="s">
+        <v>184</v>
+      </c>
+      <c r="E81" t="s">
+        <v>393</v>
+      </c>
+      <c r="F81" t="s">
+        <v>184</v>
+      </c>
+      <c r="G81" t="s">
+        <v>186</v>
+      </c>
+      <c r="H81" t="s">
+        <v>187</v>
+      </c>
+      <c r="I81" t="s">
+        <v>248</v>
+      </c>
+      <c r="J81" t="s">
+        <v>407</v>
+      </c>
+      <c r="K81" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>17</v>
+      </c>
+      <c r="B82" t="s">
+        <v>106</v>
+      </c>
+      <c r="C82">
+        <v>1</v>
+      </c>
+      <c r="D82" t="s">
+        <v>184</v>
+      </c>
+      <c r="E82" t="s">
+        <v>408</v>
+      </c>
+      <c r="F82" t="s">
+        <v>184</v>
+      </c>
+      <c r="G82" t="s">
+        <v>186</v>
+      </c>
+      <c r="H82" t="s">
+        <v>187</v>
+      </c>
+      <c r="I82" t="s">
+        <v>188</v>
+      </c>
+      <c r="J82" t="s">
+        <v>356</v>
+      </c>
+      <c r="K82" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>17</v>
+      </c>
+      <c r="B83" t="s">
+        <v>106</v>
+      </c>
+      <c r="C83">
+        <v>2</v>
+      </c>
+      <c r="D83" t="s">
+        <v>184</v>
+      </c>
+      <c r="E83" t="s">
+        <v>410</v>
+      </c>
+      <c r="F83" t="s">
+        <v>184</v>
+      </c>
+      <c r="G83" t="s">
+        <v>186</v>
+      </c>
+      <c r="H83" t="s">
+        <v>187</v>
+      </c>
+      <c r="I83" t="s">
+        <v>248</v>
+      </c>
+      <c r="J83" t="s">
+        <v>411</v>
+      </c>
+      <c r="K83" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>17</v>
+      </c>
+      <c r="B84" t="s">
+        <v>106</v>
+      </c>
+      <c r="C84">
+        <v>3</v>
+      </c>
+      <c r="D84" t="s">
+        <v>184</v>
+      </c>
+      <c r="E84" t="s">
+        <v>413</v>
+      </c>
+      <c r="F84" t="s">
+        <v>184</v>
+      </c>
+      <c r="G84" t="s">
+        <v>186</v>
+      </c>
+      <c r="H84" t="s">
+        <v>187</v>
+      </c>
+      <c r="I84" t="s">
+        <v>194</v>
+      </c>
+      <c r="J84" t="s">
+        <v>414</v>
+      </c>
+      <c r="K84" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>17</v>
+      </c>
+      <c r="B85" t="s">
+        <v>106</v>
+      </c>
+      <c r="C85">
+        <v>4</v>
+      </c>
+      <c r="D85" t="s">
+        <v>184</v>
+      </c>
+      <c r="E85" t="s">
+        <v>416</v>
+      </c>
+      <c r="F85" t="s">
+        <v>184</v>
+      </c>
+      <c r="G85" t="s">
+        <v>205</v>
+      </c>
+      <c r="H85" t="s">
+        <v>206</v>
+      </c>
+      <c r="I85" t="s">
+        <v>202</v>
+      </c>
+      <c r="J85" t="s">
+        <v>417</v>
+      </c>
+      <c r="K85" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>17</v>
+      </c>
+      <c r="B86" t="s">
+        <v>106</v>
+      </c>
+      <c r="C86">
+        <v>5</v>
+      </c>
+      <c r="D86" t="s">
+        <v>184</v>
+      </c>
+      <c r="E86" t="s">
+        <v>408</v>
+      </c>
+      <c r="F86" t="s">
+        <v>184</v>
+      </c>
+      <c r="G86" t="s">
+        <v>186</v>
+      </c>
+      <c r="H86" t="s">
+        <v>187</v>
+      </c>
+      <c r="I86" t="s">
+        <v>202</v>
+      </c>
+      <c r="J86" t="s">
+        <v>419</v>
+      </c>
+      <c r="K86" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>18</v>
+      </c>
+      <c r="B87" t="s">
+        <v>112</v>
+      </c>
+      <c r="C87">
+        <v>1</v>
+      </c>
+      <c r="D87" t="s">
+        <v>184</v>
+      </c>
+      <c r="E87" t="s">
+        <v>420</v>
+      </c>
+      <c r="F87" t="s">
+        <v>184</v>
+      </c>
+      <c r="G87" t="s">
+        <v>186</v>
+      </c>
+      <c r="H87" t="s">
+        <v>187</v>
+      </c>
+      <c r="I87" t="s">
+        <v>188</v>
+      </c>
+      <c r="J87" t="s">
+        <v>421</v>
+      </c>
+      <c r="K87" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>18</v>
+      </c>
+      <c r="B88" t="s">
+        <v>112</v>
+      </c>
+      <c r="C88">
+        <v>2</v>
+      </c>
+      <c r="D88" t="s">
+        <v>184</v>
+      </c>
+      <c r="E88" t="s">
+        <v>423</v>
+      </c>
+      <c r="F88" t="s">
+        <v>184</v>
+      </c>
+      <c r="G88" t="s">
+        <v>192</v>
+      </c>
+      <c r="H88" t="s">
+        <v>193</v>
+      </c>
+      <c r="I88" t="s">
+        <v>248</v>
+      </c>
+      <c r="J88" t="s">
+        <v>424</v>
+      </c>
+      <c r="K88" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>18</v>
+      </c>
+      <c r="B89" t="s">
+        <v>112</v>
+      </c>
+      <c r="C89">
+        <v>3</v>
+      </c>
+      <c r="D89" t="s">
+        <v>184</v>
+      </c>
+      <c r="E89" t="s">
+        <v>426</v>
+      </c>
+      <c r="F89" t="s">
+        <v>184</v>
+      </c>
+      <c r="G89" t="s">
+        <v>186</v>
+      </c>
+      <c r="H89" t="s">
+        <v>187</v>
+      </c>
+      <c r="I89" t="s">
+        <v>223</v>
+      </c>
+      <c r="J89" t="s">
+        <v>427</v>
+      </c>
+      <c r="K89" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>18</v>
+      </c>
+      <c r="B90" t="s">
+        <v>112</v>
+      </c>
+      <c r="C90">
+        <v>4</v>
+      </c>
+      <c r="D90" t="s">
+        <v>184</v>
+      </c>
+      <c r="E90" t="s">
+        <v>429</v>
+      </c>
+      <c r="F90" t="s">
+        <v>184</v>
+      </c>
+      <c r="G90" t="s">
+        <v>403</v>
+      </c>
+      <c r="H90" t="s">
+        <v>404</v>
+      </c>
+      <c r="I90" t="s">
+        <v>202</v>
+      </c>
+      <c r="J90" t="s">
+        <v>430</v>
+      </c>
+      <c r="K90" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>18</v>
+      </c>
+      <c r="B91" t="s">
+        <v>112</v>
+      </c>
+      <c r="C91">
+        <v>5</v>
+      </c>
+      <c r="D91" t="s">
+        <v>184</v>
+      </c>
+      <c r="E91" t="s">
+        <v>420</v>
+      </c>
+      <c r="F91" t="s">
+        <v>184</v>
+      </c>
+      <c r="G91" t="s">
+        <v>186</v>
+      </c>
+      <c r="H91" t="s">
+        <v>187</v>
+      </c>
+      <c r="I91" t="s">
+        <v>202</v>
+      </c>
+      <c r="J91" t="s">
+        <v>432</v>
+      </c>
+      <c r="K91" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>19</v>
+      </c>
+      <c r="B92" t="s">
+        <v>119</v>
+      </c>
+      <c r="C92">
+        <v>1</v>
+      </c>
+      <c r="D92" t="s">
+        <v>184</v>
+      </c>
+      <c r="E92" t="s">
+        <v>433</v>
+      </c>
+      <c r="F92" t="s">
+        <v>184</v>
+      </c>
+      <c r="G92" t="s">
+        <v>186</v>
+      </c>
+      <c r="H92" t="s">
+        <v>187</v>
+      </c>
+      <c r="I92" t="s">
+        <v>188</v>
+      </c>
+      <c r="J92" t="s">
+        <v>434</v>
+      </c>
+      <c r="K92" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>19</v>
+      </c>
+      <c r="B93" t="s">
+        <v>119</v>
+      </c>
+      <c r="C93">
+        <v>2</v>
+      </c>
+      <c r="D93" t="s">
+        <v>184</v>
+      </c>
+      <c r="E93" t="s">
+        <v>436</v>
+      </c>
+      <c r="F93" t="s">
+        <v>184</v>
+      </c>
+      <c r="G93" t="s">
+        <v>403</v>
+      </c>
+      <c r="H93" t="s">
+        <v>404</v>
+      </c>
+      <c r="I93" t="s">
+        <v>223</v>
+      </c>
+      <c r="J93" t="s">
+        <v>437</v>
+      </c>
+      <c r="K93" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>19</v>
+      </c>
+      <c r="B94" t="s">
+        <v>119</v>
+      </c>
+      <c r="C94">
+        <v>3</v>
+      </c>
+      <c r="D94" t="s">
+        <v>184</v>
+      </c>
+      <c r="E94" t="s">
+        <v>439</v>
+      </c>
+      <c r="F94" t="s">
+        <v>184</v>
+      </c>
+      <c r="G94" t="s">
+        <v>186</v>
+      </c>
+      <c r="H94" t="s">
+        <v>187</v>
+      </c>
+      <c r="I94" t="s">
+        <v>212</v>
+      </c>
+      <c r="J94" t="s">
+        <v>440</v>
+      </c>
+      <c r="K94" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>19</v>
+      </c>
+      <c r="B95" t="s">
+        <v>119</v>
+      </c>
+      <c r="C95">
+        <v>4</v>
+      </c>
+      <c r="D95" t="s">
+        <v>184</v>
+      </c>
+      <c r="E95" t="s">
+        <v>442</v>
+      </c>
+      <c r="F95" t="s">
+        <v>184</v>
+      </c>
+      <c r="G95" t="s">
+        <v>192</v>
+      </c>
+      <c r="H95" t="s">
+        <v>193</v>
+      </c>
+      <c r="I95" t="s">
+        <v>188</v>
+      </c>
+      <c r="J95" t="s">
+        <v>443</v>
+      </c>
+      <c r="K95" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>19</v>
+      </c>
+      <c r="B96" t="s">
+        <v>119</v>
+      </c>
+      <c r="C96">
+        <v>5</v>
+      </c>
+      <c r="D96" t="s">
+        <v>184</v>
+      </c>
+      <c r="E96" t="s">
+        <v>433</v>
+      </c>
+      <c r="F96" t="s">
+        <v>184</v>
+      </c>
+      <c r="G96" t="s">
+        <v>186</v>
+      </c>
+      <c r="H96" t="s">
+        <v>187</v>
+      </c>
+      <c r="I96" t="s">
+        <v>202</v>
+      </c>
+      <c r="J96" t="s">
+        <v>445</v>
+      </c>
+      <c r="K96" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>20</v>
+      </c>
+      <c r="B97" t="s">
+        <v>125</v>
+      </c>
+      <c r="C97">
+        <v>1</v>
+      </c>
+      <c r="D97" t="s">
+        <v>184</v>
+      </c>
+      <c r="E97" t="s">
+        <v>446</v>
+      </c>
+      <c r="F97" t="s">
+        <v>184</v>
+      </c>
+      <c r="G97" t="s">
+        <v>186</v>
+      </c>
+      <c r="H97" t="s">
+        <v>187</v>
+      </c>
+      <c r="I97" t="s">
+        <v>212</v>
+      </c>
+      <c r="J97" t="s">
+        <v>356</v>
+      </c>
+      <c r="K97" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>20</v>
+      </c>
+      <c r="B98" t="s">
+        <v>125</v>
+      </c>
+      <c r="C98">
+        <v>2</v>
+      </c>
+      <c r="D98" t="s">
+        <v>184</v>
+      </c>
+      <c r="E98" t="s">
+        <v>448</v>
+      </c>
+      <c r="F98" t="s">
+        <v>184</v>
+      </c>
+      <c r="G98" t="s">
+        <v>186</v>
+      </c>
+      <c r="H98" t="s">
+        <v>187</v>
+      </c>
+      <c r="I98" t="s">
+        <v>188</v>
+      </c>
+      <c r="J98" t="s">
+        <v>449</v>
+      </c>
+      <c r="K98" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>20</v>
+      </c>
+      <c r="B99" t="s">
+        <v>125</v>
+      </c>
+      <c r="C99">
+        <v>3</v>
+      </c>
+      <c r="D99" t="s">
+        <v>184</v>
+      </c>
+      <c r="E99" t="s">
+        <v>451</v>
+      </c>
+      <c r="F99" t="s">
+        <v>184</v>
+      </c>
+      <c r="G99" t="s">
+        <v>403</v>
+      </c>
+      <c r="H99" t="s">
+        <v>404</v>
+      </c>
+      <c r="I99" t="s">
+        <v>202</v>
+      </c>
+      <c r="J99" t="s">
+        <v>452</v>
+      </c>
+      <c r="K99" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>20</v>
+      </c>
+      <c r="B100" t="s">
+        <v>125</v>
+      </c>
+      <c r="C100">
+        <v>4</v>
+      </c>
+      <c r="D100" t="s">
+        <v>184</v>
+      </c>
+      <c r="E100" t="s">
+        <v>454</v>
+      </c>
+      <c r="F100" t="s">
+        <v>184</v>
+      </c>
+      <c r="G100" t="s">
+        <v>186</v>
+      </c>
+      <c r="H100" t="s">
+        <v>187</v>
+      </c>
+      <c r="I100" t="s">
+        <v>248</v>
+      </c>
+      <c r="J100" t="s">
+        <v>455</v>
+      </c>
+      <c r="K100" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>20</v>
+      </c>
+      <c r="B101" t="s">
+        <v>125</v>
+      </c>
+      <c r="C101">
+        <v>5</v>
+      </c>
+      <c r="D101" t="s">
+        <v>184</v>
+      </c>
+      <c r="E101" t="s">
+        <v>446</v>
+      </c>
+      <c r="F101" t="s">
+        <v>184</v>
+      </c>
+      <c r="G101" t="s">
+        <v>403</v>
+      </c>
+      <c r="H101" t="s">
+        <v>404</v>
+      </c>
+      <c r="I101" t="s">
+        <v>202</v>
+      </c>
+      <c r="J101" t="s">
+        <v>457</v>
+      </c>
+      <c r="K101" t="s">
+        <v>447</v>
       </c>
     </row>
   </sheetData>
@@ -2193,7 +6183,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -2209,10 +6199,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>196</v>
+        <v>458</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>197</v>
+        <v>459</v>
       </c>
     </row>
     <row r="2" ht="40" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2223,10 +6213,10 @@
         <v>9</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" ht="40" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2234,13 +6224,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>201</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" ht="40" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2248,13 +6238,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5" ht="40" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2262,13 +6252,237 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>205</v>
+        <v>184</v>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="8" ht="40" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="12" ht="40" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="5">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="13" ht="40" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="5">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="14" ht="40" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="5">
+        <v>13</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="15" ht="40" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="5">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="5">
+        <v>15</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="17" ht="40" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="5">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="18" ht="40" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="5">
+        <v>17</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="19" ht="40" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="5">
+        <v>18</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="20" ht="40" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="5">
+        <v>19</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="21" ht="40" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="5">
+        <v>20</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -2279,7 +6493,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -2296,10 +6510,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>206</v>
+        <v>460</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>207</v>
+        <v>461</v>
       </c>
     </row>
     <row r="2" ht="50" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2310,10 +6524,10 @@
         <v>9</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>208</v>
+        <v>184</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" ht="50" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2321,13 +6535,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>210</v>
+        <v>184</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>211</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" ht="50" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2335,13 +6549,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>212</v>
+        <v>184</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>213</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5" ht="50" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2349,13 +6563,237 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>214</v>
+        <v>184</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>215</v>
+        <v>184</v>
+      </c>
+    </row>
+    <row r="6" ht="50" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="7" ht="50" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="8" ht="50" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="9" ht="50" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="10" ht="50" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="11" ht="50" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="12" ht="50" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="5">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="13" ht="50" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="5">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="14" ht="50" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="5">
+        <v>13</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="15" ht="50" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="5">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="16" ht="50" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="5">
+        <v>15</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="17" ht="50" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="5">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="18" ht="50" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="5">
+        <v>17</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="19" ht="50" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="5">
+        <v>18</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="20" ht="50" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="5">
+        <v>19</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="21" ht="50" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="5">
+        <v>20</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>184</v>
       </c>
     </row>
   </sheetData>

--- a/personetics-demo-data.xlsx
+++ b/personetics-demo-data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="515">
   <si>
     <t>Chapter</t>
   </si>
@@ -62,40 +62,43 @@
     <t>Balance Growth, Engagement Lift</t>
   </si>
   <si>
-    <t>Becoming a teenager</t>
-  </si>
-  <si>
-    <t>First debit card issued</t>
-  </si>
-  <si>
-    <t>Age 16</t>
-  </si>
-  <si>
-    <t>Independence</t>
-  </si>
-  <si>
-    <t>Alex gets a first debit card. Every swipe is a chance to teach a money habit that lasts a lifetime.</t>
-  </si>
-  <si>
-    <t>Engagement Lift, Financial Health, Primacy</t>
-  </si>
-  <si>
-    <t>Leaving home for college</t>
-  </si>
-  <si>
-    <t>Tuition payments and student spending begin</t>
-  </si>
-  <si>
-    <t>Age 18</t>
+    <t>Smart Start Account Holder</t>
+  </si>
+  <si>
+    <t>Parents deposit pocket money into Paul's Smart Start Account</t>
+  </si>
+  <si>
+    <t>Age 11</t>
+  </si>
+  <si>
+    <t>Motivation Through Milestones</t>
+  </si>
+  <si>
+    <t>Paul is 11, uses his Smart Start account, and spends mainly on GAA equipment. BOI Buddy turns parent deposits into a weekly savings habit.</t>
+  </si>
+  <si>
+    <t>Balance Growth, Engagement Lift, Financial Health, Primacy</t>
+  </si>
+  <si>
+    <t>Transition to Student Account</t>
+  </si>
+  <si>
+    <t>BOI Buddy recommends transition from Smart Start to Student Account</t>
+  </si>
+  <si>
+    <t>Age 17</t>
   </si>
   <si>
     <t>student</t>
   </si>
   <si>
-    <t>New Chapter</t>
-  </si>
-  <si>
-    <t>Tuition, books, dorm — Alex's life turns financially complex overnight. MyBank steadies the ride.</t>
+    <t>Confidence Before Independence</t>
+  </si>
+  <si>
+    <t>Paul has transitioned to Student Account holder status after BOI Buddy analyzed his savings consistency.</t>
+  </si>
+  <si>
+    <t>Primacy, Engagement Lift, Financial Health, Retention</t>
   </si>
   <si>
     <t>Building credit</t>
@@ -137,19 +140,22 @@
     <t>Engagement Lift, Financial Health, Primacy, Card Spend</t>
   </si>
   <si>
-    <t>Starting a career</t>
-  </si>
-  <si>
-    <t>First payroll deposit detected</t>
+    <t>Early Career Salary-Rent Pattern</t>
+  </si>
+  <si>
+    <t>Monthly salary in and rent out pattern detected</t>
   </si>
   <si>
     <t>Age 23</t>
   </si>
   <si>
-    <t>A real paycheck arrives. So does the temptation to spend it. MyBank turns the moment into primacy and savings.</t>
-  </si>
-  <si>
-    <t>Balance Growth, Primacy, Financial Health</t>
+    <t>Taking Control</t>
+  </si>
+  <si>
+    <t>At 23, Paul is in early career mode. BOI Buddy sees salary-rent cadence and recommends a mortgage saver account.</t>
+  </si>
+  <si>
+    <t>Balance Growth, Product Sales, Engagement Lift, Financial Health</t>
   </si>
   <si>
     <t>Repaying student debt</t>
@@ -281,19 +287,25 @@
     <t>Balance Growth, Product Sales, Engagement Lift</t>
   </si>
   <si>
-    <t>Buying a first home</t>
-  </si>
-  <si>
-    <t>Mortgage funded, fixed costs reset</t>
+    <t>Mature Savings to ISA Recommendation</t>
+  </si>
+  <si>
+    <t>Strong savings consistency and balance growth detected</t>
   </si>
   <si>
     <t>Age 34</t>
   </si>
   <si>
-    <t>Closing day. Alex's life — and money — reshape overnight. MyBank is the calm voice through it all.</t>
-  </si>
-  <si>
-    <t>Product Sales, Engagement Lift, Retention, Primacy</t>
+    <t>midlife</t>
+  </si>
+  <si>
+    <t>Long-Term Security</t>
+  </si>
+  <si>
+    <t>By age 30/34, Paul has built strong savings habits. BOI Buddy recommends an ISA as the next logical step.</t>
+  </si>
+  <si>
+    <t>Wealth Management, Balance Growth, Engagement Lift, Retention</t>
   </si>
   <si>
     <t>Renovating the home</t>
@@ -323,9 +335,6 @@
     <t>Age 40</t>
   </si>
   <si>
-    <t>midlife</t>
-  </si>
-  <si>
     <t>Confidence</t>
   </si>
   <si>
@@ -641,102 +650,177 @@
     <t>Grandparents add €500 birthday gift.</t>
   </si>
   <si>
-    <t>First debit card activation - transaction pattern emerging</t>
-  </si>
-  <si>
-    <t>Alex opens the app, smiles at the friendly tone.</t>
-  </si>
-  <si>
-    <t>Youth engagement increased - app usage up 120%</t>
-  </si>
-  <si>
-    <t>Retail spending detected - recurring merchant patterns forming</t>
+    <t>Day 0</t>
+  </si>
+  <si>
+    <t>EUR20 pocket-money deposit posted to Paul's Smart Start account</t>
+  </si>
+  <si>
+    <t>Hey Paul! EUR20 has gone into your account. If you put EUR5 into your Smart Start Money Pot each week, you could have EUR100 by your birthday - that is a lot of GAA gear!</t>
+  </si>
+  <si>
+    <t>Paul opens the insight card and views his sports spend trend.</t>
+  </si>
+  <si>
+    <t>Early engagement with smart savings guidance.</t>
+  </si>
+  <si>
+    <t>Day 1</t>
+  </si>
+  <si>
+    <t>Savings goal suggestion accepted</t>
+  </si>
+  <si>
+    <t>BOI Buddy chat helps Paul set a birthday goal and confirms a weekly EUR5 transfer.</t>
+  </si>
+  <si>
+    <t>chatbot</t>
+  </si>
+  <si>
+    <t>Agentic Chat Experience</t>
+  </si>
+  <si>
+    <t>Paul enables weekly transfer to Smart Start Money Pot.</t>
+  </si>
+  <si>
+    <t>Goal tracker adoption increases retention and repeat deposits.</t>
+  </si>
+  <si>
+    <t>Day 3</t>
+  </si>
+  <si>
+    <t>First weekly transfer completed</t>
+  </si>
+  <si>
+    <t>You are on your way to your EUR100 birthday target. Keep going to unlock voucher rewards.</t>
+  </si>
+  <si>
+    <t>Paul keeps savings cadence active.</t>
+  </si>
+  <si>
+    <t>Consistent contribution behavior established.</t>
+  </si>
+  <si>
+    <t>Day 7</t>
+  </si>
+  <si>
+    <t>One-week savings streak</t>
+  </si>
+  <si>
+    <t>Email to parent: Paul's Smart Start goal is active and on track for birthday milestone.</t>
+  </si>
+  <si>
+    <t>Parent reinforces Paul's savings habit.</t>
+  </si>
+  <si>
+    <t>Higher household trust and account primacy.</t>
+  </si>
+  <si>
+    <t>Day 10</t>
+  </si>
+  <si>
+    <t>Strong child-saving pattern emerging</t>
+  </si>
+  <si>
+    <t>Banker prompt: Share youth savings rewards and next milestone options with family.</t>
+  </si>
+  <si>
+    <t>banker</t>
+  </si>
+  <si>
+    <t>Banker CRM Experience</t>
+  </si>
+  <si>
+    <t>Family accepts follow-up guidance.</t>
+  </si>
+  <si>
+    <t>Relationship deepens at early life stage.</t>
+  </si>
+  <si>
+    <t>Lifecycle trigger confirms Student Account suitability</t>
+  </si>
+  <si>
+    <t>Paul, based on your pattern, you are ready to move from Smart Start to Student Account.</t>
+  </si>
+  <si>
+    <t>Paul reviews transition details.</t>
+  </si>
+  <si>
+    <t>Product migration retained within BOI journey.</t>
+  </si>
+  <si>
+    <t>Budget assistant opened</t>
+  </si>
+  <si>
+    <t>BOI Buddy suggests a low monthly budget split for driving lessons and college fees.</t>
+  </si>
+  <si>
+    <t>Paul activates two starter goals.</t>
+  </si>
+  <si>
+    <t>Goal adoption drives student financial discipline.</t>
+  </si>
+  <si>
+    <t>Day 4</t>
+  </si>
+  <si>
+    <t>Week-one spend remains controlled</t>
+  </si>
+  <si>
+    <t>You are pacing well. Keep this budget to build both goals smoothly.</t>
+  </si>
+  <si>
+    <t>Paul keeps the budget active.</t>
+  </si>
+  <si>
+    <t>Reduced churn risk during transition stage.</t>
+  </si>
+  <si>
+    <t>Weekly goals report available</t>
+  </si>
+  <si>
+    <t>Email summary: progress against driving lessons and college fees targets.</t>
+  </si>
+  <si>
+    <t>cashflow_forecast</t>
+  </si>
+  <si>
+    <t>Paul and family review target pacing.</t>
+  </si>
+  <si>
+    <t>Higher confidence in proactive BOI support.</t>
+  </si>
+  <si>
+    <t>Day 12</t>
+  </si>
+  <si>
+    <t>Consistent student budget behavior</t>
+  </si>
+  <si>
+    <t>Banker prompt to refine budget and confirm next milestone amount.</t>
+  </si>
+  <si>
+    <t>Paul accepts short planning check-in.</t>
+  </si>
+  <si>
+    <t>Retention and primacy reinforced before adulthood choices.</t>
+  </si>
+  <si>
+    <t>Credit card application detected - new credit line opened</t>
+  </si>
+  <si>
+    <t>Alex reads the 60-second credit primer.</t>
+  </si>
+  <si>
+    <t>Credit utilization optimization - APR reduced by 3%</t>
+  </si>
+  <si>
+    <t>Payment history pattern emerging - on-time payments starting</t>
   </si>
   <si>
     <t>transaction_intelligence</t>
   </si>
   <si>
-    <t>Alex explores the category breakdown.</t>
-  </si>
-  <si>
-    <t>Recurring merchant alerts activated</t>
-  </si>
-  <si>
-    <t>Educational spending signal - books and school supplies</t>
-  </si>
-  <si>
-    <t>Alex confirms it, learns to recognize recurring bills.</t>
-  </si>
-  <si>
-    <t>Budget tracking enabled for education category</t>
-  </si>
-  <si>
-    <t>Social spending patterns - entertainment and dining</t>
-  </si>
-  <si>
-    <t>Alex sets a €200 'Headphones' goal.</t>
-  </si>
-  <si>
-    <t>Peer referral initiated</t>
-  </si>
-  <si>
-    <t>Alex shares the story with friends.</t>
-  </si>
-  <si>
-    <t>Tuition payment detected - large education transaction</t>
-  </si>
-  <si>
-    <t>cashflow_forecast</t>
-  </si>
-  <si>
-    <t>Alex sees a 4-month runway projection.</t>
-  </si>
-  <si>
-    <t>Cashflow forecast prevents overdraft - saves €45/month</t>
-  </si>
-  <si>
-    <t>Monthly spending volatility - college living expenses</t>
-  </si>
-  <si>
-    <t>Alex cancels 3 — saves €36/month.</t>
-  </si>
-  <si>
-    <t>Expense management features activated</t>
-  </si>
-  <si>
-    <t>Subscription service accumulation - streaming and apps</t>
-  </si>
-  <si>
-    <t>Alex adjusts spending; avoids overdraft.</t>
-  </si>
-  <si>
-    <t>Subscription optimization - €36 monthly savings identified</t>
-  </si>
-  <si>
-    <t>Travel spending pattern - trips home and campus visits</t>
-  </si>
-  <si>
-    <t>Alex auto-saves €400 on receipt.</t>
-  </si>
-  <si>
-    <t>Parent co-monitoring setup initiated</t>
-  </si>
-  <si>
-    <t>Alex screenshots and texts mom.</t>
-  </si>
-  <si>
-    <t>Credit card application detected - new credit line opened</t>
-  </si>
-  <si>
-    <t>Alex reads the 60-second credit primer.</t>
-  </si>
-  <si>
-    <t>Credit utilization optimization - APR reduced by 3%</t>
-  </si>
-  <si>
-    <t>Payment history pattern emerging - on-time payments starting</t>
-  </si>
-  <si>
     <t>Alex makes an early €50 payment.</t>
   </si>
   <si>
@@ -809,43 +893,73 @@
     <t>Alex follows the suggested budget.</t>
   </si>
   <si>
-    <t>Income stability confirmed - consistent salary deposits</t>
-  </si>
-  <si>
-    <t>Alex starts the one-tap switch.</t>
-  </si>
-  <si>
-    <t>Tax refund optimized - €2,100 additional annual income</t>
-  </si>
-  <si>
-    <t>Tax withholding optimization - W4 adjustment opportunity</t>
-  </si>
-  <si>
-    <t>Alex slows down, opens the spend breakdown.</t>
-  </si>
-  <si>
-    <t>Retirement savings plan recommended - €300/month auto-enrollment</t>
-  </si>
-  <si>
-    <t>Retirement savings signal - 401(k) eligibility reached</t>
-  </si>
-  <si>
-    <t>Alex turns on auto-save.</t>
-  </si>
-  <si>
-    <t>Benefits coverage optimized - 23% cost savings</t>
-  </si>
-  <si>
-    <t>Employee benefits enrollment - health insurance activated</t>
-  </si>
-  <si>
-    <t>Goal accepted; bumps to €75/paycheck.</t>
-  </si>
-  <si>
-    <t>Financial planning session scheduled</t>
-  </si>
-  <si>
-    <t>Alex shares the recap on social.</t>
+    <t>Salary and rent pattern validated across cycles</t>
+  </si>
+  <si>
+    <t>You now have predictable monthly surplus. This is a good time to start a Mortgage Saver account.</t>
+  </si>
+  <si>
+    <t>Paul checks 12-month projection.</t>
+  </si>
+  <si>
+    <t>Mortgage intent surfaced from real behavior.</t>
+  </si>
+  <si>
+    <t>Home deposit planner opened</t>
+  </si>
+  <si>
+    <t>BOI Buddy chat recommends a safe monthly contribution that protects Paul's rent buffer.</t>
+  </si>
+  <si>
+    <t>Paul confirms mortgage saver goal.</t>
+  </si>
+  <si>
+    <t>Goal-led pathway to future mortgage conversion.</t>
+  </si>
+  <si>
+    <t>Day 5</t>
+  </si>
+  <si>
+    <t>First post-salary transfer window</t>
+  </si>
+  <si>
+    <t>Enable salary-day+1 transfer to keep savings consistent without friction.</t>
+  </si>
+  <si>
+    <t>Paul enables automation.</t>
+  </si>
+  <si>
+    <t>Recurring deposits established.</t>
+  </si>
+  <si>
+    <t>Day 8</t>
+  </si>
+  <si>
+    <t>First contribution posted</t>
+  </si>
+  <si>
+    <t>Email summary confirms pace and projected home deposit growth path.</t>
+  </si>
+  <si>
+    <t>Paul keeps contribution level.</t>
+  </si>
+  <si>
+    <t>Persistence improved through transparent progress.</t>
+  </si>
+  <si>
+    <t>Day 15</t>
+  </si>
+  <si>
+    <t>Sustained saver behavior detected</t>
+  </si>
+  <si>
+    <t>Banker prompt: offer pre-mortgage readiness checklist and timeline advice.</t>
+  </si>
+  <si>
+    <t>Paul books planning review.</t>
+  </si>
+  <si>
+    <t>Higher chance of BOI mortgage origination.</t>
   </si>
   <si>
     <t>Loan servicer consolidation opportunity detected</t>
@@ -1118,43 +1232,70 @@
     <t>Alex feels confident, stays the course.</t>
   </si>
   <si>
-    <t>Mortgage application submitted - underwriting in progress</t>
-  </si>
-  <si>
-    <t>Alex follows the 5-card homeowner story.</t>
-  </si>
-  <si>
-    <t>Mortgage funded - €300K loan at 4.2% APR</t>
-  </si>
-  <si>
-    <t>Closing date scheduled - 45 days to completion</t>
-  </si>
-  <si>
-    <t>Alex accepts the new budget.</t>
-  </si>
-  <si>
-    <t>Home insurance secured - €1,200/year bundled rate</t>
-  </si>
-  <si>
-    <t>Home insurance quotes received - coverage options compared</t>
-  </si>
-  <si>
-    <t>Auto-save scheduled.</t>
-  </si>
-  <si>
-    <t>Homeownership begins - asset building accelerates</t>
-  </si>
-  <si>
-    <t>Property tax and HOA analysis completed</t>
-  </si>
-  <si>
-    <t>Alex switches.</t>
-  </si>
-  <si>
-    <t>Wealth trajectory improves - real estate equity grows</t>
-  </si>
-  <si>
-    <t>Alex feels capable.</t>
+    <t>Savings pattern reaches ISA threshold</t>
+  </si>
+  <si>
+    <t>You have developed strong savings habits. An ISA could support your next stage of growth.</t>
+  </si>
+  <si>
+    <t>Paul opens ISA explanation.</t>
+  </si>
+  <si>
+    <t>Wealth journey initiated.</t>
+  </si>
+  <si>
+    <t>ISA planner started</t>
+  </si>
+  <si>
+    <t>BOI Buddy maps ISA contributions to personal goals and sets manageable monthly pacing.</t>
+  </si>
+  <si>
+    <t>Paul activates goal-linked ISA contribution plan.</t>
+  </si>
+  <si>
+    <t>Personetics goals tooling drives product conversion.</t>
+  </si>
+  <si>
+    <t>Day 6</t>
+  </si>
+  <si>
+    <t>Scheduled monthly ISA date approaching</t>
+  </si>
+  <si>
+    <t>Reminder: staying consistent protects long-term ISA outcomes.</t>
+  </si>
+  <si>
+    <t>Paul confirms transfer.</t>
+  </si>
+  <si>
+    <t>Contribution consistency maintained.</t>
+  </si>
+  <si>
+    <t>First cycle complete</t>
+  </si>
+  <si>
+    <t>Email provides contribution summary and projection against long-term goals.</t>
+  </si>
+  <si>
+    <t>Paul reviews projection with partner.</t>
+  </si>
+  <si>
+    <t>Household confidence and retention rise.</t>
+  </si>
+  <si>
+    <t>Day 20</t>
+  </si>
+  <si>
+    <t>Steady ISA behavior confirmed</t>
+  </si>
+  <si>
+    <t>Banker prompt: offer annual optimization review and milestone planning.</t>
+  </si>
+  <si>
+    <t>Paul books annual review.</t>
+  </si>
+  <si>
+    <t>Long-term wealth relationship deepened.</t>
   </si>
   <si>
     <t>Home improvement spending detected - construction loans available</t>
@@ -1226,12 +1367,6 @@
     <t>Executive benefits available - stock options and deferred comp</t>
   </si>
   <si>
-    <t>banker</t>
-  </si>
-  <si>
-    <t>Banker CRM Experience</t>
-  </si>
-  <si>
     <t>Alex books a call.</t>
   </si>
   <si>
@@ -1395,6 +1530,38 @@
   </si>
   <si>
     <t>MyBank Capabilities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parent pocket-money deposit detected
+Sports spend pattern on GAA equipment
+Weekly transfer potential for savings habit</t>
+  </si>
+  <si>
+    <t>transaction_intelligence, personalized_insights, goals_trackers, smart_savings, engagement_builder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Healthy savings pattern over prior period
+Approaching student life stage
+Budget readiness for lessons and education costs</t>
+  </si>
+  <si>
+    <t>transaction_intelligence, personalized_insights, goals_trackers, cashflow_forecast, engagement_builder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stable monthly salary inflow
+Recurring rent outflow
+Positive surplus after essentials</t>
+  </si>
+  <si>
+    <t>cashflow_forecast, personalized_insights, goals_trackers, smart_savings, engagement_builder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consistent savings over long period
+Growing average balances
+Low missed-transfer behavior</t>
+  </si>
+  <si>
+    <t>personalized_insights, goals_trackers, cashflow_forecast, smart_savings, engagement_builder</t>
   </si>
   <si>
     <t>Bank Story</t>
@@ -1907,7 +2074,7 @@
         <v>16</v>
       </c>
       <c r="D3">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
         <v>17</v>
@@ -1936,7 +2103,7 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E4" t="s">
         <v>23</v>
@@ -1951,7 +2118,7 @@
         <v>26</v>
       </c>
       <c r="I4" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -1959,28 +2126,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5">
         <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5" t="s">
         <v>24</v>
       </c>
       <c r="G5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -1988,28 +2155,28 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D6">
         <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -2017,28 +2184,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D7">
         <v>23</v>
       </c>
       <c r="E7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G7" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="H7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -2046,28 +2213,28 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D8">
         <v>23</v>
       </c>
       <c r="E8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -2075,28 +2242,28 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D9">
         <v>24</v>
       </c>
       <c r="E9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H9" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -2104,28 +2271,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D10">
         <v>25</v>
       </c>
       <c r="E10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H10" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I10" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -2133,28 +2300,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D11">
         <v>25</v>
       </c>
       <c r="E11" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -2162,28 +2329,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D12">
         <v>27</v>
       </c>
       <c r="E12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F12" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H12" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I12" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -2191,28 +2358,28 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D13">
         <v>30</v>
       </c>
       <c r="E13" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F13" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H13" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I13" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -2220,28 +2387,28 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C14" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D14">
         <v>32</v>
       </c>
       <c r="E14" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G14" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H14" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I14" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -2249,28 +2416,28 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C15" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D15">
         <v>34</v>
       </c>
       <c r="E15" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F15" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="G15" t="s">
-        <v>37</v>
+        <v>94</v>
       </c>
       <c r="H15" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="I15" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -2278,28 +2445,28 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C16" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D16">
         <v>37</v>
       </c>
       <c r="E16" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F16" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G16" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="H16" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I16" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -2307,28 +2474,28 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C17" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D17">
         <v>40</v>
       </c>
       <c r="E17" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="F17" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="G17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H17" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="I17" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -2336,28 +2503,28 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C18" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D18">
         <v>45</v>
       </c>
       <c r="E18" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F18" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="G18" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="H18" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="I18" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -2365,28 +2532,28 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C19" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D19">
         <v>55</v>
       </c>
       <c r="E19" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F19" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G19" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="H19" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="I19" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -2394,28 +2561,28 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C20" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D20">
         <v>65</v>
       </c>
       <c r="E20" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F20" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G20" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H20" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="I20" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -2423,28 +2590,28 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C21" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D21">
         <v>72</v>
       </c>
       <c r="E21" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F21" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="G21" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H21" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="I21" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -2466,156 +2633,156 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D2" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D4" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C5" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D5" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B6" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C6" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D6" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B7" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C7" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D7" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B8" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C8" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D8" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B9" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C9" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D9" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B10" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C10" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D10" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B11" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C11" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D11" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -2648,31 +2815,31 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -2686,28 +2853,28 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="J2" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="K2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -2721,28 +2888,28 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F3" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G3" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H3" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="I3" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="J3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="K3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -2756,28 +2923,28 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E4" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F4" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G4" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H4" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I4" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="J4" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="K4" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -2791,28 +2958,28 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E5" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G5" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H5" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="I5" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="J5" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="K5" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -2826,28 +2993,28 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E6" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F6" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H6" t="s">
+        <v>209</v>
+      </c>
+      <c r="I6" t="s">
         <v>205</v>
       </c>
-      <c r="H6" t="s">
-        <v>206</v>
-      </c>
-      <c r="I6" t="s">
-        <v>202</v>
-      </c>
       <c r="J6" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="K6" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -2861,28 +3028,28 @@
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="E7" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="F7" t="s">
-        <v>184</v>
+        <v>213</v>
       </c>
       <c r="G7" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="H7" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="I7" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="J7" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="K7" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -2896,28 +3063,28 @@
         <v>2</v>
       </c>
       <c r="D8" t="s">
-        <v>184</v>
+        <v>216</v>
       </c>
       <c r="E8" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="F8" t="s">
-        <v>184</v>
+        <v>218</v>
       </c>
       <c r="G8" t="s">
-        <v>186</v>
+        <v>219</v>
       </c>
       <c r="H8" t="s">
-        <v>187</v>
+        <v>220</v>
       </c>
       <c r="I8" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="J8" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="K8" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -2931,28 +3098,28 @@
         <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>184</v>
+        <v>223</v>
       </c>
       <c r="E9" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="F9" t="s">
-        <v>184</v>
+        <v>225</v>
       </c>
       <c r="G9" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H9" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="I9" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="J9" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="K9" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -2966,28 +3133,28 @@
         <v>4</v>
       </c>
       <c r="D10" t="s">
-        <v>184</v>
+        <v>228</v>
       </c>
       <c r="E10" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="F10" t="s">
-        <v>184</v>
+        <v>230</v>
       </c>
       <c r="G10" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="H10" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="I10" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="J10" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="K10" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -3001,28 +3168,28 @@
         <v>5</v>
       </c>
       <c r="D11" t="s">
-        <v>184</v>
+        <v>233</v>
       </c>
       <c r="E11" t="s">
-        <v>208</v>
+        <v>234</v>
       </c>
       <c r="F11" t="s">
-        <v>184</v>
+        <v>235</v>
       </c>
       <c r="G11" t="s">
-        <v>186</v>
+        <v>236</v>
       </c>
       <c r="H11" t="s">
-        <v>187</v>
+        <v>237</v>
       </c>
       <c r="I11" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="J11" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="K11" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -3036,28 +3203,28 @@
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="E12" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="F12" t="s">
-        <v>184</v>
+        <v>241</v>
       </c>
       <c r="G12" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H12" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I12" t="s">
-        <v>223</v>
+        <v>191</v>
       </c>
       <c r="J12" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="K12" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -3071,28 +3238,28 @@
         <v>2</v>
       </c>
       <c r="D13" t="s">
-        <v>184</v>
+        <v>216</v>
       </c>
       <c r="E13" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="F13" t="s">
-        <v>184</v>
+        <v>245</v>
       </c>
       <c r="G13" t="s">
-        <v>192</v>
+        <v>219</v>
       </c>
       <c r="H13" t="s">
-        <v>193</v>
+        <v>220</v>
       </c>
       <c r="I13" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="J13" t="s">
-        <v>227</v>
+        <v>246</v>
       </c>
       <c r="K13" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -3106,28 +3273,28 @@
         <v>3</v>
       </c>
       <c r="D14" t="s">
-        <v>184</v>
+        <v>248</v>
       </c>
       <c r="E14" t="s">
-        <v>229</v>
+        <v>249</v>
       </c>
       <c r="F14" t="s">
-        <v>184</v>
+        <v>250</v>
       </c>
       <c r="G14" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H14" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="I14" t="s">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="J14" t="s">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="K14" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -3141,28 +3308,28 @@
         <v>4</v>
       </c>
       <c r="D15" t="s">
-        <v>184</v>
+        <v>228</v>
       </c>
       <c r="E15" t="s">
-        <v>232</v>
+        <v>253</v>
       </c>
       <c r="F15" t="s">
-        <v>184</v>
+        <v>254</v>
       </c>
       <c r="G15" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="H15" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="I15" t="s">
-        <v>198</v>
+        <v>255</v>
       </c>
       <c r="J15" t="s">
-        <v>233</v>
+        <v>256</v>
       </c>
       <c r="K15" t="s">
-        <v>234</v>
+        <v>257</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -3176,28 +3343,28 @@
         <v>5</v>
       </c>
       <c r="D16" t="s">
-        <v>184</v>
+        <v>258</v>
       </c>
       <c r="E16" t="s">
-        <v>222</v>
+        <v>259</v>
       </c>
       <c r="F16" t="s">
-        <v>184</v>
+        <v>260</v>
       </c>
       <c r="G16" t="s">
-        <v>186</v>
+        <v>236</v>
       </c>
       <c r="H16" t="s">
-        <v>187</v>
+        <v>237</v>
       </c>
       <c r="I16" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="J16" t="s">
-        <v>235</v>
+        <v>261</v>
       </c>
       <c r="K16" t="s">
-        <v>225</v>
+        <v>262</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -3205,34 +3372,34 @@
         <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
       <c r="D17" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E17" t="s">
-        <v>236</v>
+        <v>263</v>
       </c>
       <c r="F17" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G17" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H17" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I17" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="J17" t="s">
-        <v>237</v>
+        <v>264</v>
       </c>
       <c r="K17" t="s">
-        <v>238</v>
+        <v>265</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -3240,34 +3407,34 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C18">
         <v>2</v>
       </c>
       <c r="D18" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E18" t="s">
-        <v>239</v>
+        <v>266</v>
       </c>
       <c r="F18" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G18" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H18" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="I18" t="s">
-        <v>212</v>
+        <v>267</v>
       </c>
       <c r="J18" t="s">
-        <v>240</v>
+        <v>268</v>
       </c>
       <c r="K18" t="s">
-        <v>241</v>
+        <v>269</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -3275,34 +3442,34 @@
         <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C19">
         <v>3</v>
       </c>
       <c r="D19" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E19" t="s">
-        <v>242</v>
+        <v>270</v>
       </c>
       <c r="F19" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G19" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H19" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I19" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="J19" t="s">
-        <v>243</v>
+        <v>271</v>
       </c>
       <c r="K19" t="s">
-        <v>244</v>
+        <v>272</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -3310,34 +3477,34 @@
         <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C20">
         <v>4</v>
       </c>
       <c r="D20" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E20" t="s">
-        <v>245</v>
+        <v>273</v>
       </c>
       <c r="F20" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G20" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H20" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="I20" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="J20" t="s">
-        <v>246</v>
+        <v>274</v>
       </c>
       <c r="K20" t="s">
-        <v>247</v>
+        <v>275</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -3345,34 +3512,34 @@
         <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21">
         <v>5</v>
       </c>
       <c r="D21" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E21" t="s">
-        <v>236</v>
+        <v>263</v>
       </c>
       <c r="F21" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G21" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H21" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I21" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="J21" t="s">
-        <v>249</v>
+        <v>277</v>
       </c>
       <c r="K21" t="s">
-        <v>238</v>
+        <v>265</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -3380,34 +3547,34 @@
         <v>5</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E22" t="s">
-        <v>250</v>
+        <v>278</v>
       </c>
       <c r="F22" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G22" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H22" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="J22" t="s">
-        <v>251</v>
+        <v>279</v>
       </c>
       <c r="K22" t="s">
-        <v>252</v>
+        <v>280</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -3415,34 +3582,34 @@
         <v>5</v>
       </c>
       <c r="B23" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C23">
         <v>2</v>
       </c>
       <c r="D23" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E23" t="s">
-        <v>253</v>
+        <v>281</v>
       </c>
       <c r="F23" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G23" t="s">
+        <v>208</v>
+      </c>
+      <c r="H23" t="s">
+        <v>209</v>
+      </c>
+      <c r="I23" t="s">
         <v>205</v>
       </c>
-      <c r="H23" t="s">
-        <v>206</v>
-      </c>
-      <c r="I23" t="s">
-        <v>202</v>
-      </c>
       <c r="J23" t="s">
-        <v>254</v>
+        <v>282</v>
       </c>
       <c r="K23" t="s">
-        <v>255</v>
+        <v>283</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -3450,34 +3617,34 @@
         <v>5</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C24">
         <v>3</v>
       </c>
       <c r="D24" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E24" t="s">
-        <v>256</v>
+        <v>284</v>
       </c>
       <c r="F24" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G24" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H24" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="I24" t="s">
-        <v>223</v>
+        <v>255</v>
       </c>
       <c r="J24" t="s">
-        <v>257</v>
+        <v>285</v>
       </c>
       <c r="K24" t="s">
-        <v>258</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -3485,34 +3652,34 @@
         <v>5</v>
       </c>
       <c r="B25" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C25">
         <v>4</v>
       </c>
       <c r="D25" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E25" t="s">
-        <v>259</v>
+        <v>287</v>
       </c>
       <c r="F25" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G25" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H25" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I25" t="s">
-        <v>260</v>
+        <v>288</v>
       </c>
       <c r="J25" t="s">
-        <v>261</v>
+        <v>289</v>
       </c>
       <c r="K25" t="s">
-        <v>262</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -3520,34 +3687,34 @@
         <v>5</v>
       </c>
       <c r="B26" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C26">
         <v>5</v>
       </c>
       <c r="D26" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E26" t="s">
-        <v>250</v>
+        <v>278</v>
       </c>
       <c r="F26" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G26" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H26" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I26" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="J26" t="s">
-        <v>263</v>
+        <v>291</v>
       </c>
       <c r="K26" t="s">
-        <v>252</v>
+        <v>280</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -3555,34 +3722,34 @@
         <v>6</v>
       </c>
       <c r="B27" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C27">
         <v>1</v>
       </c>
       <c r="D27" t="s">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="E27" t="s">
-        <v>264</v>
+        <v>292</v>
       </c>
       <c r="F27" t="s">
-        <v>184</v>
+        <v>293</v>
       </c>
       <c r="G27" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="H27" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="I27" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="J27" t="s">
-        <v>265</v>
+        <v>294</v>
       </c>
       <c r="K27" t="s">
-        <v>266</v>
+        <v>295</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -3590,34 +3757,34 @@
         <v>6</v>
       </c>
       <c r="B28" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C28">
         <v>2</v>
       </c>
       <c r="D28" t="s">
-        <v>184</v>
+        <v>216</v>
       </c>
       <c r="E28" t="s">
-        <v>267</v>
+        <v>296</v>
       </c>
       <c r="F28" t="s">
-        <v>184</v>
+        <v>297</v>
       </c>
       <c r="G28" t="s">
-        <v>192</v>
+        <v>219</v>
       </c>
       <c r="H28" t="s">
-        <v>193</v>
+        <v>220</v>
       </c>
       <c r="I28" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="J28" t="s">
-        <v>268</v>
+        <v>298</v>
       </c>
       <c r="K28" t="s">
-        <v>269</v>
+        <v>299</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -3625,34 +3792,34 @@
         <v>6</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C29">
         <v>3</v>
       </c>
       <c r="D29" t="s">
-        <v>184</v>
+        <v>300</v>
       </c>
       <c r="E29" t="s">
-        <v>270</v>
+        <v>301</v>
       </c>
       <c r="F29" t="s">
-        <v>184</v>
+        <v>302</v>
       </c>
       <c r="G29" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="H29" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="I29" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="J29" t="s">
-        <v>271</v>
+        <v>303</v>
       </c>
       <c r="K29" t="s">
-        <v>272</v>
+        <v>304</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -3660,34 +3827,34 @@
         <v>6</v>
       </c>
       <c r="B30" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C30">
         <v>4</v>
       </c>
       <c r="D30" t="s">
-        <v>184</v>
+        <v>305</v>
       </c>
       <c r="E30" t="s">
-        <v>273</v>
+        <v>306</v>
       </c>
       <c r="F30" t="s">
-        <v>184</v>
+        <v>307</v>
       </c>
       <c r="G30" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="H30" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="I30" t="s">
-        <v>194</v>
+        <v>255</v>
       </c>
       <c r="J30" t="s">
-        <v>274</v>
+        <v>308</v>
       </c>
       <c r="K30" t="s">
-        <v>275</v>
+        <v>309</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -3695,34 +3862,34 @@
         <v>6</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C31">
         <v>5</v>
       </c>
       <c r="D31" t="s">
-        <v>184</v>
+        <v>310</v>
       </c>
       <c r="E31" t="s">
-        <v>264</v>
+        <v>311</v>
       </c>
       <c r="F31" t="s">
-        <v>184</v>
+        <v>312</v>
       </c>
       <c r="G31" t="s">
-        <v>186</v>
+        <v>236</v>
       </c>
       <c r="H31" t="s">
-        <v>187</v>
+        <v>237</v>
       </c>
       <c r="I31" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="J31" t="s">
-        <v>276</v>
+        <v>313</v>
       </c>
       <c r="K31" t="s">
-        <v>266</v>
+        <v>314</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -3730,34 +3897,34 @@
         <v>7</v>
       </c>
       <c r="B32" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C32">
         <v>1</v>
       </c>
       <c r="D32" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E32" t="s">
-        <v>277</v>
+        <v>315</v>
       </c>
       <c r="F32" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G32" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H32" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I32" t="s">
-        <v>223</v>
+        <v>255</v>
       </c>
       <c r="J32" t="s">
-        <v>278</v>
+        <v>316</v>
       </c>
       <c r="K32" t="s">
-        <v>279</v>
+        <v>317</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -3765,34 +3932,34 @@
         <v>7</v>
       </c>
       <c r="B33" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C33">
         <v>2</v>
       </c>
       <c r="D33" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E33" t="s">
-        <v>280</v>
+        <v>318</v>
       </c>
       <c r="F33" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G33" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H33" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="I33" t="s">
-        <v>223</v>
+        <v>255</v>
       </c>
       <c r="J33" t="s">
-        <v>281</v>
+        <v>319</v>
       </c>
       <c r="K33" t="s">
-        <v>282</v>
+        <v>320</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
@@ -3800,34 +3967,34 @@
         <v>7</v>
       </c>
       <c r="B34" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C34">
         <v>3</v>
       </c>
       <c r="D34" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E34" t="s">
-        <v>283</v>
+        <v>321</v>
       </c>
       <c r="F34" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G34" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H34" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I34" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="J34" t="s">
-        <v>284</v>
+        <v>322</v>
       </c>
       <c r="K34" t="s">
-        <v>285</v>
+        <v>323</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
@@ -3835,34 +4002,34 @@
         <v>7</v>
       </c>
       <c r="B35" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C35">
         <v>4</v>
       </c>
       <c r="D35" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E35" t="s">
-        <v>286</v>
+        <v>324</v>
       </c>
       <c r="F35" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G35" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H35" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I35" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="J35" t="s">
-        <v>287</v>
+        <v>325</v>
       </c>
       <c r="K35" t="s">
-        <v>288</v>
+        <v>326</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -3870,34 +4037,34 @@
         <v>7</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C36">
         <v>5</v>
       </c>
       <c r="D36" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E36" t="s">
-        <v>277</v>
+        <v>315</v>
       </c>
       <c r="F36" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G36" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H36" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="I36" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="J36" t="s">
-        <v>289</v>
+        <v>327</v>
       </c>
       <c r="K36" t="s">
-        <v>279</v>
+        <v>317</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
@@ -3905,34 +4072,34 @@
         <v>8</v>
       </c>
       <c r="B37" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C37">
         <v>1</v>
       </c>
       <c r="D37" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E37" t="s">
-        <v>290</v>
+        <v>328</v>
       </c>
       <c r="F37" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G37" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H37" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I37" t="s">
-        <v>212</v>
+        <v>267</v>
       </c>
       <c r="J37" t="s">
-        <v>291</v>
+        <v>329</v>
       </c>
       <c r="K37" t="s">
-        <v>292</v>
+        <v>330</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -3940,34 +4107,34 @@
         <v>8</v>
       </c>
       <c r="B38" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C38">
         <v>2</v>
       </c>
       <c r="D38" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E38" t="s">
-        <v>293</v>
+        <v>331</v>
       </c>
       <c r="F38" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G38" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H38" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I38" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="J38" t="s">
-        <v>294</v>
+        <v>332</v>
       </c>
       <c r="K38" t="s">
-        <v>295</v>
+        <v>333</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -3975,34 +4142,34 @@
         <v>8</v>
       </c>
       <c r="B39" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C39">
         <v>3</v>
       </c>
       <c r="D39" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E39" t="s">
-        <v>296</v>
+        <v>334</v>
       </c>
       <c r="F39" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G39" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H39" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I39" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="J39" t="s">
-        <v>297</v>
+        <v>335</v>
       </c>
       <c r="K39" t="s">
-        <v>298</v>
+        <v>336</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
@@ -4010,34 +4177,34 @@
         <v>8</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C40">
         <v>4</v>
       </c>
       <c r="D40" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E40" t="s">
-        <v>299</v>
+        <v>337</v>
       </c>
       <c r="F40" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G40" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H40" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="I40" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="J40" t="s">
-        <v>300</v>
+        <v>338</v>
       </c>
       <c r="K40" t="s">
-        <v>301</v>
+        <v>339</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
@@ -4045,34 +4212,34 @@
         <v>8</v>
       </c>
       <c r="B41" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C41">
         <v>5</v>
       </c>
       <c r="D41" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E41" t="s">
-        <v>290</v>
+        <v>328</v>
       </c>
       <c r="F41" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G41" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H41" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="I41" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="J41" t="s">
-        <v>302</v>
+        <v>340</v>
       </c>
       <c r="K41" t="s">
-        <v>292</v>
+        <v>330</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
@@ -4080,34 +4247,34 @@
         <v>9</v>
       </c>
       <c r="B42" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C42">
         <v>1</v>
       </c>
       <c r="D42" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E42" t="s">
-        <v>303</v>
+        <v>341</v>
       </c>
       <c r="F42" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G42" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H42" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="I42" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="J42" t="s">
-        <v>304</v>
+        <v>342</v>
       </c>
       <c r="K42" t="s">
-        <v>305</v>
+        <v>343</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
@@ -4115,34 +4282,34 @@
         <v>9</v>
       </c>
       <c r="B43" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C43">
         <v>2</v>
       </c>
       <c r="D43" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E43" t="s">
-        <v>306</v>
+        <v>344</v>
       </c>
       <c r="F43" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G43" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H43" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I43" t="s">
-        <v>223</v>
+        <v>255</v>
       </c>
       <c r="J43" t="s">
-        <v>307</v>
+        <v>345</v>
       </c>
       <c r="K43" t="s">
-        <v>308</v>
+        <v>346</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
@@ -4150,34 +4317,34 @@
         <v>9</v>
       </c>
       <c r="B44" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C44">
         <v>3</v>
       </c>
       <c r="D44" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E44" t="s">
-        <v>309</v>
+        <v>347</v>
       </c>
       <c r="F44" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G44" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H44" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I44" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="J44" t="s">
-        <v>310</v>
+        <v>348</v>
       </c>
       <c r="K44" t="s">
-        <v>311</v>
+        <v>349</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
@@ -4185,34 +4352,34 @@
         <v>9</v>
       </c>
       <c r="B45" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C45">
         <v>4</v>
       </c>
       <c r="D45" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E45" t="s">
-        <v>312</v>
+        <v>350</v>
       </c>
       <c r="F45" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G45" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="H45" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="I45" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="J45" t="s">
-        <v>313</v>
+        <v>351</v>
       </c>
       <c r="K45" t="s">
-        <v>314</v>
+        <v>352</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
@@ -4220,34 +4387,34 @@
         <v>9</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C46">
         <v>5</v>
       </c>
       <c r="D46" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E46" t="s">
-        <v>303</v>
+        <v>341</v>
       </c>
       <c r="F46" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G46" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H46" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="I46" t="s">
-        <v>223</v>
+        <v>255</v>
       </c>
       <c r="J46" t="s">
-        <v>315</v>
+        <v>353</v>
       </c>
       <c r="K46" t="s">
-        <v>305</v>
+        <v>343</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
@@ -4255,34 +4422,34 @@
         <v>10</v>
       </c>
       <c r="B47" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C47">
         <v>1</v>
       </c>
       <c r="D47" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E47" t="s">
-        <v>316</v>
+        <v>354</v>
       </c>
       <c r="F47" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G47" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H47" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="I47" t="s">
-        <v>212</v>
+        <v>267</v>
       </c>
       <c r="J47" t="s">
-        <v>317</v>
+        <v>355</v>
       </c>
       <c r="K47" t="s">
-        <v>318</v>
+        <v>356</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
@@ -4290,34 +4457,34 @@
         <v>10</v>
       </c>
       <c r="B48" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C48">
         <v>2</v>
       </c>
       <c r="D48" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E48" t="s">
-        <v>319</v>
+        <v>357</v>
       </c>
       <c r="F48" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G48" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H48" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I48" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="J48" t="s">
-        <v>320</v>
+        <v>358</v>
       </c>
       <c r="K48" t="s">
-        <v>321</v>
+        <v>359</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
@@ -4325,34 +4492,34 @@
         <v>10</v>
       </c>
       <c r="B49" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C49">
         <v>3</v>
       </c>
       <c r="D49" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E49" t="s">
-        <v>322</v>
+        <v>360</v>
       </c>
       <c r="F49" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G49" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H49" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I49" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="J49" t="s">
-        <v>323</v>
+        <v>361</v>
       </c>
       <c r="K49" t="s">
-        <v>324</v>
+        <v>362</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
@@ -4360,34 +4527,34 @@
         <v>10</v>
       </c>
       <c r="B50" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C50">
         <v>4</v>
       </c>
       <c r="D50" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E50" t="s">
-        <v>325</v>
+        <v>363</v>
       </c>
       <c r="F50" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G50" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H50" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="I50" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="J50" t="s">
-        <v>326</v>
+        <v>364</v>
       </c>
       <c r="K50" t="s">
-        <v>327</v>
+        <v>365</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
@@ -4395,34 +4562,34 @@
         <v>10</v>
       </c>
       <c r="B51" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C51">
         <v>5</v>
       </c>
       <c r="D51" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E51" t="s">
-        <v>316</v>
+        <v>354</v>
       </c>
       <c r="F51" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G51" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H51" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I51" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="J51" t="s">
-        <v>328</v>
+        <v>366</v>
       </c>
       <c r="K51" t="s">
-        <v>318</v>
+        <v>356</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
@@ -4430,34 +4597,34 @@
         <v>11</v>
       </c>
       <c r="B52" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C52">
         <v>1</v>
       </c>
       <c r="D52" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E52" t="s">
-        <v>329</v>
+        <v>367</v>
       </c>
       <c r="F52" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G52" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H52" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="I52" t="s">
-        <v>212</v>
+        <v>267</v>
       </c>
       <c r="J52" t="s">
-        <v>330</v>
+        <v>368</v>
       </c>
       <c r="K52" t="s">
-        <v>331</v>
+        <v>369</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -4465,34 +4632,34 @@
         <v>11</v>
       </c>
       <c r="B53" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C53">
         <v>2</v>
       </c>
       <c r="D53" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E53" t="s">
-        <v>332</v>
+        <v>370</v>
       </c>
       <c r="F53" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G53" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H53" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I53" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="J53" t="s">
-        <v>333</v>
+        <v>371</v>
       </c>
       <c r="K53" t="s">
-        <v>334</v>
+        <v>372</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
@@ -4500,34 +4667,34 @@
         <v>11</v>
       </c>
       <c r="B54" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C54">
         <v>3</v>
       </c>
       <c r="D54" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E54" t="s">
-        <v>335</v>
+        <v>373</v>
       </c>
       <c r="F54" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G54" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H54" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I54" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="J54" t="s">
-        <v>336</v>
+        <v>374</v>
       </c>
       <c r="K54" t="s">
-        <v>337</v>
+        <v>375</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
@@ -4535,34 +4702,34 @@
         <v>11</v>
       </c>
       <c r="B55" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C55">
         <v>4</v>
       </c>
       <c r="D55" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E55" t="s">
-        <v>338</v>
+        <v>376</v>
       </c>
       <c r="F55" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G55" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H55" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I55" t="s">
-        <v>212</v>
+        <v>267</v>
       </c>
       <c r="J55" t="s">
-        <v>339</v>
+        <v>377</v>
       </c>
       <c r="K55" t="s">
-        <v>340</v>
+        <v>378</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -4570,34 +4737,34 @@
         <v>11</v>
       </c>
       <c r="B56" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C56">
         <v>5</v>
       </c>
       <c r="D56" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E56" t="s">
-        <v>329</v>
+        <v>367</v>
       </c>
       <c r="F56" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G56" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="H56" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="I56" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="J56" t="s">
-        <v>341</v>
+        <v>379</v>
       </c>
       <c r="K56" t="s">
-        <v>331</v>
+        <v>369</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
@@ -4605,34 +4772,34 @@
         <v>12</v>
       </c>
       <c r="B57" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C57">
         <v>1</v>
       </c>
       <c r="D57" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E57" t="s">
-        <v>342</v>
+        <v>380</v>
       </c>
       <c r="F57" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G57" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H57" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I57" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="J57" t="s">
-        <v>343</v>
+        <v>381</v>
       </c>
       <c r="K57" t="s">
-        <v>344</v>
+        <v>382</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
@@ -4640,34 +4807,34 @@
         <v>12</v>
       </c>
       <c r="B58" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C58">
         <v>2</v>
       </c>
       <c r="D58" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E58" t="s">
-        <v>345</v>
+        <v>383</v>
       </c>
       <c r="F58" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G58" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H58" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="I58" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="J58" t="s">
-        <v>346</v>
+        <v>384</v>
       </c>
       <c r="K58" t="s">
-        <v>347</v>
+        <v>385</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
@@ -4675,34 +4842,34 @@
         <v>12</v>
       </c>
       <c r="B59" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C59">
         <v>3</v>
       </c>
       <c r="D59" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E59" t="s">
-        <v>348</v>
+        <v>386</v>
       </c>
       <c r="F59" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G59" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H59" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I59" t="s">
-        <v>223</v>
+        <v>255</v>
       </c>
       <c r="J59" t="s">
-        <v>349</v>
+        <v>387</v>
       </c>
       <c r="K59" t="s">
-        <v>350</v>
+        <v>388</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
@@ -4710,34 +4877,34 @@
         <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C60">
         <v>4</v>
       </c>
       <c r="D60" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E60" t="s">
-        <v>351</v>
+        <v>389</v>
       </c>
       <c r="F60" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G60" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H60" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I60" t="s">
-        <v>212</v>
+        <v>267</v>
       </c>
       <c r="J60" t="s">
-        <v>352</v>
+        <v>390</v>
       </c>
       <c r="K60" t="s">
-        <v>353</v>
+        <v>391</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
@@ -4745,34 +4912,34 @@
         <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C61">
         <v>5</v>
       </c>
       <c r="D61" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E61" t="s">
-        <v>342</v>
+        <v>380</v>
       </c>
       <c r="F61" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G61" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H61" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="I61" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="J61" t="s">
-        <v>354</v>
+        <v>392</v>
       </c>
       <c r="K61" t="s">
-        <v>344</v>
+        <v>382</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
@@ -4780,34 +4947,34 @@
         <v>13</v>
       </c>
       <c r="B62" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C62">
         <v>1</v>
       </c>
       <c r="D62" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E62" t="s">
-        <v>355</v>
+        <v>393</v>
       </c>
       <c r="F62" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G62" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H62" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I62" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="J62" t="s">
-        <v>356</v>
+        <v>394</v>
       </c>
       <c r="K62" t="s">
-        <v>357</v>
+        <v>395</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
@@ -4815,34 +4982,34 @@
         <v>13</v>
       </c>
       <c r="B63" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C63">
         <v>2</v>
       </c>
       <c r="D63" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E63" t="s">
-        <v>358</v>
+        <v>396</v>
       </c>
       <c r="F63" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G63" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H63" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I63" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="J63" t="s">
-        <v>297</v>
+        <v>335</v>
       </c>
       <c r="K63" t="s">
-        <v>359</v>
+        <v>397</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
@@ -4850,34 +5017,34 @@
         <v>13</v>
       </c>
       <c r="B64" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C64">
         <v>3</v>
       </c>
       <c r="D64" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E64" t="s">
-        <v>360</v>
+        <v>398</v>
       </c>
       <c r="F64" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G64" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H64" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I64" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="J64" t="s">
-        <v>361</v>
+        <v>399</v>
       </c>
       <c r="K64" t="s">
-        <v>362</v>
+        <v>400</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
@@ -4885,34 +5052,34 @@
         <v>13</v>
       </c>
       <c r="B65" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C65">
         <v>4</v>
       </c>
       <c r="D65" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E65" t="s">
-        <v>363</v>
+        <v>401</v>
       </c>
       <c r="F65" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G65" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H65" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="I65" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="J65" t="s">
-        <v>364</v>
+        <v>402</v>
       </c>
       <c r="K65" t="s">
-        <v>365</v>
+        <v>403</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
@@ -4920,34 +5087,34 @@
         <v>13</v>
       </c>
       <c r="B66" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C66">
         <v>5</v>
       </c>
       <c r="D66" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E66" t="s">
-        <v>355</v>
+        <v>393</v>
       </c>
       <c r="F66" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G66" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H66" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I66" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="J66" t="s">
-        <v>366</v>
+        <v>404</v>
       </c>
       <c r="K66" t="s">
-        <v>357</v>
+        <v>395</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
@@ -4955,34 +5122,34 @@
         <v>14</v>
       </c>
       <c r="B67" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C67">
         <v>1</v>
       </c>
       <c r="D67" t="s">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="E67" t="s">
-        <v>367</v>
+        <v>405</v>
       </c>
       <c r="F67" t="s">
-        <v>184</v>
+        <v>406</v>
       </c>
       <c r="G67" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H67" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I67" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="J67" t="s">
-        <v>368</v>
+        <v>407</v>
       </c>
       <c r="K67" t="s">
-        <v>369</v>
+        <v>408</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
@@ -4990,34 +5157,34 @@
         <v>14</v>
       </c>
       <c r="B68" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C68">
         <v>2</v>
       </c>
       <c r="D68" t="s">
-        <v>184</v>
+        <v>216</v>
       </c>
       <c r="E68" t="s">
-        <v>370</v>
+        <v>409</v>
       </c>
       <c r="F68" t="s">
-        <v>184</v>
+        <v>410</v>
       </c>
       <c r="G68" t="s">
-        <v>186</v>
+        <v>219</v>
       </c>
       <c r="H68" t="s">
-        <v>187</v>
+        <v>220</v>
       </c>
       <c r="I68" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="J68" t="s">
-        <v>371</v>
+        <v>411</v>
       </c>
       <c r="K68" t="s">
-        <v>372</v>
+        <v>412</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
@@ -5025,34 +5192,34 @@
         <v>14</v>
       </c>
       <c r="B69" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C69">
         <v>3</v>
       </c>
       <c r="D69" t="s">
-        <v>184</v>
+        <v>413</v>
       </c>
       <c r="E69" t="s">
-        <v>373</v>
+        <v>414</v>
       </c>
       <c r="F69" t="s">
-        <v>184</v>
+        <v>415</v>
       </c>
       <c r="G69" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H69" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="I69" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="J69" t="s">
-        <v>374</v>
+        <v>416</v>
       </c>
       <c r="K69" t="s">
-        <v>375</v>
+        <v>417</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
@@ -5060,34 +5227,34 @@
         <v>14</v>
       </c>
       <c r="B70" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C70">
         <v>4</v>
       </c>
       <c r="D70" t="s">
-        <v>184</v>
+        <v>233</v>
       </c>
       <c r="E70" t="s">
-        <v>376</v>
+        <v>418</v>
       </c>
       <c r="F70" t="s">
-        <v>184</v>
+        <v>419</v>
       </c>
       <c r="G70" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="H70" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="I70" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="J70" t="s">
-        <v>377</v>
+        <v>420</v>
       </c>
       <c r="K70" t="s">
-        <v>378</v>
+        <v>421</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
@@ -5095,34 +5262,34 @@
         <v>14</v>
       </c>
       <c r="B71" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C71">
         <v>5</v>
       </c>
       <c r="D71" t="s">
-        <v>184</v>
+        <v>422</v>
       </c>
       <c r="E71" t="s">
-        <v>367</v>
+        <v>423</v>
       </c>
       <c r="F71" t="s">
-        <v>184</v>
+        <v>424</v>
       </c>
       <c r="G71" t="s">
-        <v>186</v>
+        <v>236</v>
       </c>
       <c r="H71" t="s">
-        <v>187</v>
+        <v>237</v>
       </c>
       <c r="I71" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="J71" t="s">
-        <v>379</v>
+        <v>425</v>
       </c>
       <c r="K71" t="s">
-        <v>369</v>
+        <v>426</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
@@ -5130,34 +5297,34 @@
         <v>15</v>
       </c>
       <c r="B72" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C72">
         <v>1</v>
       </c>
       <c r="D72" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E72" t="s">
-        <v>380</v>
+        <v>427</v>
       </c>
       <c r="F72" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G72" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H72" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I72" t="s">
-        <v>212</v>
+        <v>267</v>
       </c>
       <c r="J72" t="s">
-        <v>381</v>
+        <v>428</v>
       </c>
       <c r="K72" t="s">
-        <v>382</v>
+        <v>429</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
@@ -5165,34 +5332,34 @@
         <v>15</v>
       </c>
       <c r="B73" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C73">
         <v>2</v>
       </c>
       <c r="D73" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E73" t="s">
-        <v>383</v>
+        <v>430</v>
       </c>
       <c r="F73" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G73" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H73" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="I73" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="J73" t="s">
-        <v>384</v>
+        <v>431</v>
       </c>
       <c r="K73" t="s">
-        <v>385</v>
+        <v>432</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
@@ -5200,34 +5367,34 @@
         <v>15</v>
       </c>
       <c r="B74" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C74">
         <v>3</v>
       </c>
       <c r="D74" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E74" t="s">
-        <v>386</v>
+        <v>433</v>
       </c>
       <c r="F74" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G74" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H74" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I74" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="J74" t="s">
-        <v>387</v>
+        <v>434</v>
       </c>
       <c r="K74" t="s">
-        <v>388</v>
+        <v>435</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
@@ -5235,34 +5402,34 @@
         <v>15</v>
       </c>
       <c r="B75" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C75">
         <v>4</v>
       </c>
       <c r="D75" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E75" t="s">
-        <v>389</v>
+        <v>436</v>
       </c>
       <c r="F75" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G75" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H75" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I75" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="J75" t="s">
-        <v>390</v>
+        <v>437</v>
       </c>
       <c r="K75" t="s">
-        <v>391</v>
+        <v>438</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
@@ -5270,34 +5437,34 @@
         <v>15</v>
       </c>
       <c r="B76" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C76">
         <v>5</v>
       </c>
       <c r="D76" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E76" t="s">
-        <v>380</v>
+        <v>427</v>
       </c>
       <c r="F76" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G76" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H76" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I76" t="s">
-        <v>212</v>
+        <v>267</v>
       </c>
       <c r="J76" t="s">
-        <v>392</v>
+        <v>439</v>
       </c>
       <c r="K76" t="s">
-        <v>382</v>
+        <v>429</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
@@ -5305,34 +5472,34 @@
         <v>16</v>
       </c>
       <c r="B77" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C77">
         <v>1</v>
       </c>
       <c r="D77" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E77" t="s">
-        <v>393</v>
+        <v>440</v>
       </c>
       <c r="F77" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G77" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H77" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I77" t="s">
-        <v>212</v>
+        <v>267</v>
       </c>
       <c r="J77" t="s">
-        <v>394</v>
+        <v>441</v>
       </c>
       <c r="K77" t="s">
-        <v>395</v>
+        <v>442</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
@@ -5340,34 +5507,34 @@
         <v>16</v>
       </c>
       <c r="B78" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C78">
         <v>2</v>
       </c>
       <c r="D78" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E78" t="s">
-        <v>396</v>
+        <v>443</v>
       </c>
       <c r="F78" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G78" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H78" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="I78" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="J78" t="s">
-        <v>397</v>
+        <v>444</v>
       </c>
       <c r="K78" t="s">
-        <v>398</v>
+        <v>445</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
@@ -5375,34 +5542,34 @@
         <v>16</v>
       </c>
       <c r="B79" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C79">
         <v>3</v>
       </c>
       <c r="D79" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E79" t="s">
-        <v>399</v>
+        <v>446</v>
       </c>
       <c r="F79" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G79" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H79" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I79" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="J79" t="s">
-        <v>400</v>
+        <v>447</v>
       </c>
       <c r="K79" t="s">
-        <v>401</v>
+        <v>448</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
@@ -5410,34 +5577,34 @@
         <v>16</v>
       </c>
       <c r="B80" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C80">
         <v>4</v>
       </c>
       <c r="D80" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E80" t="s">
-        <v>402</v>
+        <v>449</v>
       </c>
       <c r="F80" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G80" t="s">
-        <v>403</v>
+        <v>236</v>
       </c>
       <c r="H80" t="s">
-        <v>404</v>
+        <v>237</v>
       </c>
       <c r="I80" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="J80" t="s">
-        <v>405</v>
+        <v>450</v>
       </c>
       <c r="K80" t="s">
-        <v>406</v>
+        <v>451</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
@@ -5445,34 +5612,34 @@
         <v>16</v>
       </c>
       <c r="B81" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C81">
         <v>5</v>
       </c>
       <c r="D81" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E81" t="s">
-        <v>393</v>
+        <v>440</v>
       </c>
       <c r="F81" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G81" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H81" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I81" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="J81" t="s">
-        <v>407</v>
+        <v>452</v>
       </c>
       <c r="K81" t="s">
-        <v>395</v>
+        <v>442</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -5480,34 +5647,34 @@
         <v>17</v>
       </c>
       <c r="B82" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C82">
         <v>1</v>
       </c>
       <c r="D82" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E82" t="s">
-        <v>408</v>
+        <v>453</v>
       </c>
       <c r="F82" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G82" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H82" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I82" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="J82" t="s">
-        <v>356</v>
+        <v>394</v>
       </c>
       <c r="K82" t="s">
-        <v>409</v>
+        <v>454</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
@@ -5515,34 +5682,34 @@
         <v>17</v>
       </c>
       <c r="B83" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C83">
         <v>2</v>
       </c>
       <c r="D83" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E83" t="s">
-        <v>410</v>
+        <v>455</v>
       </c>
       <c r="F83" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G83" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H83" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I83" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="J83" t="s">
-        <v>411</v>
+        <v>456</v>
       </c>
       <c r="K83" t="s">
-        <v>412</v>
+        <v>457</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
@@ -5550,34 +5717,34 @@
         <v>17</v>
       </c>
       <c r="B84" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C84">
         <v>3</v>
       </c>
       <c r="D84" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E84" t="s">
-        <v>413</v>
+        <v>458</v>
       </c>
       <c r="F84" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G84" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H84" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I84" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="J84" t="s">
-        <v>414</v>
+        <v>459</v>
       </c>
       <c r="K84" t="s">
-        <v>415</v>
+        <v>460</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
@@ -5585,34 +5752,34 @@
         <v>17</v>
       </c>
       <c r="B85" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C85">
         <v>4</v>
       </c>
       <c r="D85" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E85" t="s">
-        <v>416</v>
+        <v>461</v>
       </c>
       <c r="F85" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G85" t="s">
+        <v>208</v>
+      </c>
+      <c r="H85" t="s">
+        <v>209</v>
+      </c>
+      <c r="I85" t="s">
         <v>205</v>
       </c>
-      <c r="H85" t="s">
-        <v>206</v>
-      </c>
-      <c r="I85" t="s">
-        <v>202</v>
-      </c>
       <c r="J85" t="s">
-        <v>417</v>
+        <v>462</v>
       </c>
       <c r="K85" t="s">
-        <v>418</v>
+        <v>463</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
@@ -5620,34 +5787,34 @@
         <v>17</v>
       </c>
       <c r="B86" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C86">
         <v>5</v>
       </c>
       <c r="D86" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E86" t="s">
-        <v>408</v>
+        <v>453</v>
       </c>
       <c r="F86" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G86" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H86" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I86" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="J86" t="s">
-        <v>419</v>
+        <v>464</v>
       </c>
       <c r="K86" t="s">
-        <v>409</v>
+        <v>454</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
@@ -5655,34 +5822,34 @@
         <v>18</v>
       </c>
       <c r="B87" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C87">
         <v>1</v>
       </c>
       <c r="D87" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E87" t="s">
-        <v>420</v>
+        <v>465</v>
       </c>
       <c r="F87" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G87" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H87" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I87" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="J87" t="s">
-        <v>421</v>
+        <v>466</v>
       </c>
       <c r="K87" t="s">
-        <v>422</v>
+        <v>467</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
@@ -5690,34 +5857,34 @@
         <v>18</v>
       </c>
       <c r="B88" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C88">
         <v>2</v>
       </c>
       <c r="D88" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E88" t="s">
-        <v>423</v>
+        <v>468</v>
       </c>
       <c r="F88" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G88" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H88" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="I88" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="J88" t="s">
-        <v>424</v>
+        <v>469</v>
       </c>
       <c r="K88" t="s">
-        <v>425</v>
+        <v>470</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
@@ -5725,34 +5892,34 @@
         <v>18</v>
       </c>
       <c r="B89" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C89">
         <v>3</v>
       </c>
       <c r="D89" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E89" t="s">
-        <v>426</v>
+        <v>471</v>
       </c>
       <c r="F89" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G89" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H89" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I89" t="s">
-        <v>223</v>
+        <v>255</v>
       </c>
       <c r="J89" t="s">
-        <v>427</v>
+        <v>472</v>
       </c>
       <c r="K89" t="s">
-        <v>428</v>
+        <v>473</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
@@ -5760,34 +5927,34 @@
         <v>18</v>
       </c>
       <c r="B90" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C90">
         <v>4</v>
       </c>
       <c r="D90" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E90" t="s">
-        <v>429</v>
+        <v>474</v>
       </c>
       <c r="F90" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G90" t="s">
-        <v>403</v>
+        <v>236</v>
       </c>
       <c r="H90" t="s">
-        <v>404</v>
+        <v>237</v>
       </c>
       <c r="I90" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="J90" t="s">
-        <v>430</v>
+        <v>475</v>
       </c>
       <c r="K90" t="s">
-        <v>431</v>
+        <v>476</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
@@ -5795,34 +5962,34 @@
         <v>18</v>
       </c>
       <c r="B91" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C91">
         <v>5</v>
       </c>
       <c r="D91" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E91" t="s">
-        <v>420</v>
+        <v>465</v>
       </c>
       <c r="F91" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G91" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H91" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I91" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="J91" t="s">
-        <v>432</v>
+        <v>477</v>
       </c>
       <c r="K91" t="s">
-        <v>422</v>
+        <v>467</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
@@ -5830,34 +5997,34 @@
         <v>19</v>
       </c>
       <c r="B92" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C92">
         <v>1</v>
       </c>
       <c r="D92" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E92" t="s">
-        <v>433</v>
+        <v>478</v>
       </c>
       <c r="F92" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G92" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H92" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I92" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="J92" t="s">
-        <v>434</v>
+        <v>479</v>
       </c>
       <c r="K92" t="s">
-        <v>435</v>
+        <v>480</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
@@ -5865,34 +6032,34 @@
         <v>19</v>
       </c>
       <c r="B93" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C93">
         <v>2</v>
       </c>
       <c r="D93" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E93" t="s">
-        <v>436</v>
+        <v>481</v>
       </c>
       <c r="F93" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G93" t="s">
-        <v>403</v>
+        <v>236</v>
       </c>
       <c r="H93" t="s">
-        <v>404</v>
+        <v>237</v>
       </c>
       <c r="I93" t="s">
-        <v>223</v>
+        <v>255</v>
       </c>
       <c r="J93" t="s">
-        <v>437</v>
+        <v>482</v>
       </c>
       <c r="K93" t="s">
-        <v>438</v>
+        <v>483</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
@@ -5900,34 +6067,34 @@
         <v>19</v>
       </c>
       <c r="B94" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C94">
         <v>3</v>
       </c>
       <c r="D94" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E94" t="s">
-        <v>439</v>
+        <v>484</v>
       </c>
       <c r="F94" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G94" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H94" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I94" t="s">
-        <v>212</v>
+        <v>267</v>
       </c>
       <c r="J94" t="s">
-        <v>440</v>
+        <v>485</v>
       </c>
       <c r="K94" t="s">
-        <v>441</v>
+        <v>486</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
@@ -5935,34 +6102,34 @@
         <v>19</v>
       </c>
       <c r="B95" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C95">
         <v>4</v>
       </c>
       <c r="D95" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E95" t="s">
-        <v>442</v>
+        <v>487</v>
       </c>
       <c r="F95" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G95" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H95" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="I95" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="J95" t="s">
-        <v>443</v>
+        <v>488</v>
       </c>
       <c r="K95" t="s">
-        <v>444</v>
+        <v>489</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
@@ -5970,34 +6137,34 @@
         <v>19</v>
       </c>
       <c r="B96" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C96">
         <v>5</v>
       </c>
       <c r="D96" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E96" t="s">
-        <v>433</v>
+        <v>478</v>
       </c>
       <c r="F96" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G96" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H96" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I96" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="J96" t="s">
-        <v>445</v>
+        <v>490</v>
       </c>
       <c r="K96" t="s">
-        <v>435</v>
+        <v>480</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
@@ -6005,34 +6172,34 @@
         <v>20</v>
       </c>
       <c r="B97" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C97">
         <v>1</v>
       </c>
       <c r="D97" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E97" t="s">
-        <v>446</v>
+        <v>491</v>
       </c>
       <c r="F97" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G97" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H97" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I97" t="s">
-        <v>212</v>
+        <v>267</v>
       </c>
       <c r="J97" t="s">
-        <v>356</v>
+        <v>394</v>
       </c>
       <c r="K97" t="s">
-        <v>447</v>
+        <v>492</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
@@ -6040,34 +6207,34 @@
         <v>20</v>
       </c>
       <c r="B98" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C98">
         <v>2</v>
       </c>
       <c r="D98" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E98" t="s">
-        <v>448</v>
+        <v>493</v>
       </c>
       <c r="F98" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G98" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H98" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I98" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="J98" t="s">
-        <v>449</v>
+        <v>494</v>
       </c>
       <c r="K98" t="s">
-        <v>450</v>
+        <v>495</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
@@ -6075,34 +6242,34 @@
         <v>20</v>
       </c>
       <c r="B99" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C99">
         <v>3</v>
       </c>
       <c r="D99" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E99" t="s">
-        <v>451</v>
+        <v>496</v>
       </c>
       <c r="F99" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G99" t="s">
-        <v>403</v>
+        <v>236</v>
       </c>
       <c r="H99" t="s">
-        <v>404</v>
+        <v>237</v>
       </c>
       <c r="I99" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="J99" t="s">
-        <v>452</v>
+        <v>497</v>
       </c>
       <c r="K99" t="s">
-        <v>453</v>
+        <v>498</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
@@ -6110,34 +6277,34 @@
         <v>20</v>
       </c>
       <c r="B100" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C100">
         <v>4</v>
       </c>
       <c r="D100" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E100" t="s">
-        <v>454</v>
+        <v>499</v>
       </c>
       <c r="F100" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G100" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H100" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I100" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="J100" t="s">
-        <v>455</v>
+        <v>500</v>
       </c>
       <c r="K100" t="s">
-        <v>456</v>
+        <v>501</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
@@ -6145,34 +6312,34 @@
         <v>20</v>
       </c>
       <c r="B101" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C101">
         <v>5</v>
       </c>
       <c r="D101" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E101" t="s">
-        <v>446</v>
+        <v>491</v>
       </c>
       <c r="F101" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G101" t="s">
-        <v>403</v>
+        <v>236</v>
       </c>
       <c r="H101" t="s">
-        <v>404</v>
+        <v>237</v>
       </c>
       <c r="I101" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="J101" t="s">
-        <v>457</v>
+        <v>502</v>
       </c>
       <c r="K101" t="s">
-        <v>447</v>
+        <v>492</v>
       </c>
     </row>
   </sheetData>
@@ -6199,10 +6366,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>458</v>
+        <v>503</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>459</v>
+        <v>504</v>
       </c>
     </row>
     <row r="2" ht="40" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -6213,10 +6380,10 @@
         <v>9</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" ht="40" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -6227,10 +6394,10 @@
         <v>15</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>184</v>
+        <v>505</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>184</v>
+        <v>506</v>
       </c>
     </row>
     <row r="4" ht="40" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -6241,10 +6408,10 @@
         <v>21</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>184</v>
+        <v>507</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>184</v>
+        <v>508</v>
       </c>
     </row>
     <row r="5" ht="40" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -6252,13 +6419,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" ht="40" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -6266,13 +6433,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" ht="40" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -6280,13 +6447,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>184</v>
+        <v>509</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>184</v>
+        <v>510</v>
       </c>
     </row>
     <row r="8" ht="40" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -6294,13 +6461,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" ht="40" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -6308,13 +6475,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10" ht="40" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -6322,13 +6489,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11" ht="40" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -6336,13 +6503,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" ht="40" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -6350,13 +6517,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13" ht="40" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -6364,13 +6531,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14" ht="40" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -6378,13 +6545,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="15" ht="40" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -6392,13 +6559,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>184</v>
+        <v>511</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>184</v>
+        <v>512</v>
       </c>
     </row>
     <row r="16" ht="40" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -6406,13 +6573,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="17" ht="40" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -6420,13 +6587,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="18" ht="40" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -6434,13 +6601,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="19" ht="40" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -6448,13 +6615,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="20" ht="40" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -6462,13 +6629,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="21" ht="40" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -6476,13 +6643,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -6510,10 +6677,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>460</v>
+        <v>513</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>461</v>
+        <v>514</v>
       </c>
     </row>
     <row r="2" ht="50" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -6524,10 +6691,10 @@
         <v>9</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" ht="50" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -6538,10 +6705,10 @@
         <v>15</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" ht="50" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -6552,10 +6719,10 @@
         <v>21</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" ht="50" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -6563,13 +6730,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" ht="50" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -6577,13 +6744,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" ht="50" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -6591,13 +6758,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" ht="50" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -6605,13 +6772,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" ht="50" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -6619,13 +6786,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10" ht="50" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -6633,13 +6800,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11" ht="50" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -6647,13 +6814,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" ht="50" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -6661,13 +6828,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13" ht="50" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -6675,13 +6842,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14" ht="50" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -6689,13 +6856,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="15" ht="50" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -6703,13 +6870,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="16" ht="50" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -6717,13 +6884,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="17" ht="50" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -6731,13 +6898,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="18" ht="50" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -6745,13 +6912,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="19" ht="50" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -6759,13 +6926,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="20" ht="50" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -6773,13 +6940,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="21" ht="50" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -6787,13 +6954,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>

--- a/personetics-demo-data.xlsx
+++ b/personetics-demo-data.xlsx
@@ -469,7 +469,7 @@
         <v>Smart Start Account Holder</v>
       </c>
       <c r="C3" t="str">
-        <v>First debit card issued and activated for youth savings</v>
+        <v>Parents deposit pocket money into Paul's Smart Start Account</v>
       </c>
       <c r="D3">
         <v>11</v>
@@ -484,7 +484,7 @@
         <v>Motivation &amp; Goal Achievement</v>
       </c>
       <c r="H3" t="str">
-        <v>Paul receives a Smart Start Account from BOI and his parents deposit EUR20 pocket money. With a goal to save EUR100 for GAA equipment by his birthday, Paul learns the power of consistent saving.</v>
+        <v>Paul is 11, loves sport, and regularly spends on GAA equipment. When his parents lodge €20 into his Smart Start Account, BOI Buddy nudges him toward a €100 birthday savings goal.</v>
       </c>
       <c r="I3" t="str">
         <v>Engagement Lift, Financial Health, Primacy</v>
@@ -1416,10 +1416,10 @@
         <v/>
       </c>
       <c r="E7" t="str">
-        <v>Parents deposit EUR20 pocket money - savings goal opportunity</v>
+        <v>Parents deposit pocket money into Paul's Smart Start Account</v>
       </c>
       <c r="F7" t="str">
-        <v>Hey Paul! EUR20 has gone into your account. If you put EUR5 into your Smart Start Money Pot each week, you could have EUR100 by your birthday - that's a lot of GAA gear! If you reach this savings goal, you can earn points to redeem vouchers.</v>
+        <v>Hey Paul! €20 has gone into your account. If you put €5 into your Smart Start Money Pot each week, you could have €100 by your birthday - that's a lot of GAA gear! If you reach this savings goal, you can earn points to redeem vouchers.</v>
       </c>
       <c r="G7" t="str">
         <v>chatbot</v>
@@ -1431,7 +1431,7 @@
         <v>goals_trackers</v>
       </c>
       <c r="J7" t="str">
-        <v>Paul starts his Smart Start Money Pot and begins working toward his EUR100 birthday goal.</v>
+        <v>Paul can see he is already on his way to hitting his €100 birthday goal for new GAA gear.</v>
       </c>
       <c r="K7" t="str">
         <v>Goal tracker adoption increases youth engagement and repeat deposits</v>
@@ -1457,7 +1457,7 @@
         <v>Weekly pocket money habit forming - consistent savings behaviour detected</v>
       </c>
       <c r="F8" t="str">
-        <v>You are one week into your savings plan. Another EUR5 moved into your Money Pot today, so you are already building momentum toward your birthday target.</v>
+        <v>You are one week into your savings plan. Another €5 moved into your Money Pot today, so you are already building momentum toward your birthday target.</v>
       </c>
       <c r="G8" t="str">
         <v>in_app</v>
@@ -1495,7 +1495,7 @@
         <v>Birthday target projection updated - goal remains on track</v>
       </c>
       <c r="F9" t="str">
-        <v>At your current pace, you are still on track to reach EUR100 by your birthday. Keep going and you will be ready for new GAA gear right on time.</v>
+        <v>At your current pace, you are still on track to reach €100 by your birthday. Keep going and you will be ready for new GAA gear right on time.</v>
       </c>
       <c r="G9" t="str">
         <v>push</v>
@@ -1533,7 +1533,7 @@
         <v>Reward threshold approaching - loyalty incentive available</v>
       </c>
       <c r="F10" t="str">
-        <v>You are close to your EUR100 goal. One more good week of saving could unlock reward points that can be redeemed for vouchers.</v>
+        <v>You are close to your €100 goal. One more good week of saving could unlock reward points that can be redeemed for vouchers.</v>
       </c>
       <c r="G10" t="str">
         <v>in_app</v>
@@ -1571,7 +1571,7 @@
         <v>Savings goal achieved - celebration and follow-on habit opportunity</v>
       </c>
       <c r="F11" t="str">
-        <v>You did it, Paul. Your Smart Start Money Pot has reached EUR100 in time for your birthday. Keep the habit going and choose your next savings goal.</v>
+        <v>You did it, Paul. Your Smart Start Money Pot has reached €100 in time for your birthday. Keep the habit going and choose your next savings goal.</v>
       </c>
       <c r="G11" t="str">
         <v>in_app</v>
@@ -1583,7 +1583,7 @@
         <v>goals_trackers</v>
       </c>
       <c r="J11" t="str">
-        <v>Paul reaches his EUR100 goal and feels proud that his saving habit paid off.</v>
+        <v>Paul reaches his €100 goal and feels proud that his saving habit paid off.</v>
       </c>
       <c r="K11" t="str">
         <v>Goal completion improves retention and creates momentum for the next savings objective</v>
